--- a/docs/2026-참석자명단/참가자DB_및_참석자명단.xlsx
+++ b/docs/2026-참석자명단/참가자DB_및_참석자명단.xlsx
@@ -559,7 +559,7 @@
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>① 창업특강_참석  9. 28.(월) 특강 참석자 — 현장 서명부를 받아 옮겨 적는 시트</t>
+          <t>① 창업특강_참석  9. 28.(월) 특강 참석자 — 현장 서명부를 받아 옮겨 적는 시트 (200행)</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
     <row r="11">
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>③ 서류심사_결과  예선 평가 점수와 합격 여부</t>
+          <t>③ 서류심사_결과  심사위원 2인의 항목별 점수 — 소계·평균 자동 계산, 합격 여부</t>
         </is>
       </c>
     </row>
@@ -665,26 +665,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:J202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>※ 9. 28.(월) 현장 서명부(창업특강_참석자명단.pdf)를 받아 이곳에 옮겨 적습니다.</t>
+          <t>※ 9. 28.(월) 14:00~16:00 현장 서명부(창업특강_참석자명단.pdf)를 받아 이곳에 옮겨 적습니다.</t>
         </is>
       </c>
     </row>
@@ -701,47 +700,42 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>소속 대학</t>
+          <t>소속</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>학과</t>
+          <t>학년</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>학년</t>
+          <t>학번</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>학번</t>
+          <t>연락처</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>연락처</t>
+          <t>이메일</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>이메일</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>개인정보
 동의</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>서명
 확인</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -760,7 +754,6 @@
       <c r="H3" s="7" t="n"/>
       <c r="I3" s="7" t="n"/>
       <c r="J3" s="7" t="n"/>
-      <c r="K3" s="7" t="n"/>
     </row>
     <row r="4" ht="19" customHeight="1">
       <c r="A4" s="8" t="n">
@@ -775,7 +768,6 @@
       <c r="H4" s="9" t="n"/>
       <c r="I4" s="9" t="n"/>
       <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
     </row>
     <row r="5" ht="19" customHeight="1">
       <c r="A5" s="6" t="n">
@@ -790,7 +782,6 @@
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
       <c r="J5" s="7" t="n"/>
-      <c r="K5" s="7" t="n"/>
     </row>
     <row r="6" ht="19" customHeight="1">
       <c r="A6" s="8" t="n">
@@ -805,7 +796,6 @@
       <c r="H6" s="9" t="n"/>
       <c r="I6" s="9" t="n"/>
       <c r="J6" s="9" t="n"/>
-      <c r="K6" s="9" t="n"/>
     </row>
     <row r="7" ht="19" customHeight="1">
       <c r="A7" s="6" t="n">
@@ -820,7 +810,6 @@
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
       <c r="J7" s="7" t="n"/>
-      <c r="K7" s="7" t="n"/>
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="8" t="n">
@@ -835,7 +824,6 @@
       <c r="H8" s="9" t="n"/>
       <c r="I8" s="9" t="n"/>
       <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" s="6" t="n">
@@ -850,7 +838,6 @@
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n"/>
       <c r="J9" s="7" t="n"/>
-      <c r="K9" s="7" t="n"/>
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="8" t="n">
@@ -865,7 +852,6 @@
       <c r="H10" s="9" t="n"/>
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="6" t="n">
@@ -880,7 +866,6 @@
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
       <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="8" t="n">
@@ -895,7 +880,6 @@
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="9" t="n"/>
       <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n"/>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="6" t="n">
@@ -910,7 +894,6 @@
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="7" t="n"/>
       <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="8" t="n">
@@ -925,7 +908,6 @@
       <c r="H14" s="9" t="n"/>
       <c r="I14" s="9" t="n"/>
       <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="6" t="n">
@@ -940,7 +922,6 @@
       <c r="H15" s="7" t="n"/>
       <c r="I15" s="7" t="n"/>
       <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="8" t="n">
@@ -955,7 +936,6 @@
       <c r="H16" s="9" t="n"/>
       <c r="I16" s="9" t="n"/>
       <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="6" t="n">
@@ -970,7 +950,6 @@
       <c r="H17" s="7" t="n"/>
       <c r="I17" s="7" t="n"/>
       <c r="J17" s="7" t="n"/>
-      <c r="K17" s="7" t="n"/>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="8" t="n">
@@ -985,7 +964,6 @@
       <c r="H18" s="9" t="n"/>
       <c r="I18" s="9" t="n"/>
       <c r="J18" s="9" t="n"/>
-      <c r="K18" s="9" t="n"/>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="6" t="n">
@@ -1000,7 +978,6 @@
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="7" t="n"/>
       <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="8" t="n">
@@ -1015,7 +992,6 @@
       <c r="H20" s="9" t="n"/>
       <c r="I20" s="9" t="n"/>
       <c r="J20" s="9" t="n"/>
-      <c r="K20" s="9" t="n"/>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="6" t="n">
@@ -1030,7 +1006,6 @@
       <c r="H21" s="7" t="n"/>
       <c r="I21" s="7" t="n"/>
       <c r="J21" s="7" t="n"/>
-      <c r="K21" s="7" t="n"/>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="8" t="n">
@@ -1045,7 +1020,6 @@
       <c r="H22" s="9" t="n"/>
       <c r="I22" s="9" t="n"/>
       <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="6" t="n">
@@ -1060,7 +1034,6 @@
       <c r="H23" s="7" t="n"/>
       <c r="I23" s="7" t="n"/>
       <c r="J23" s="7" t="n"/>
-      <c r="K23" s="7" t="n"/>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="8" t="n">
@@ -1075,7 +1048,6 @@
       <c r="H24" s="9" t="n"/>
       <c r="I24" s="9" t="n"/>
       <c r="J24" s="9" t="n"/>
-      <c r="K24" s="9" t="n"/>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="6" t="n">
@@ -1090,7 +1062,6 @@
       <c r="H25" s="7" t="n"/>
       <c r="I25" s="7" t="n"/>
       <c r="J25" s="7" t="n"/>
-      <c r="K25" s="7" t="n"/>
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="8" t="n">
@@ -1105,7 +1076,6 @@
       <c r="H26" s="9" t="n"/>
       <c r="I26" s="9" t="n"/>
       <c r="J26" s="9" t="n"/>
-      <c r="K26" s="9" t="n"/>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="6" t="n">
@@ -1120,7 +1090,6 @@
       <c r="H27" s="7" t="n"/>
       <c r="I27" s="7" t="n"/>
       <c r="J27" s="7" t="n"/>
-      <c r="K27" s="7" t="n"/>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="8" t="n">
@@ -1135,7 +1104,6 @@
       <c r="H28" s="9" t="n"/>
       <c r="I28" s="9" t="n"/>
       <c r="J28" s="9" t="n"/>
-      <c r="K28" s="9" t="n"/>
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="6" t="n">
@@ -1150,7 +1118,6 @@
       <c r="H29" s="7" t="n"/>
       <c r="I29" s="7" t="n"/>
       <c r="J29" s="7" t="n"/>
-      <c r="K29" s="7" t="n"/>
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="8" t="n">
@@ -1165,7 +1132,6 @@
       <c r="H30" s="9" t="n"/>
       <c r="I30" s="9" t="n"/>
       <c r="J30" s="9" t="n"/>
-      <c r="K30" s="9" t="n"/>
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="6" t="n">
@@ -1180,7 +1146,6 @@
       <c r="H31" s="7" t="n"/>
       <c r="I31" s="7" t="n"/>
       <c r="J31" s="7" t="n"/>
-      <c r="K31" s="7" t="n"/>
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="8" t="n">
@@ -1195,7 +1160,6 @@
       <c r="H32" s="9" t="n"/>
       <c r="I32" s="9" t="n"/>
       <c r="J32" s="9" t="n"/>
-      <c r="K32" s="9" t="n"/>
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="6" t="n">
@@ -1210,7 +1174,6 @@
       <c r="H33" s="7" t="n"/>
       <c r="I33" s="7" t="n"/>
       <c r="J33" s="7" t="n"/>
-      <c r="K33" s="7" t="n"/>
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="8" t="n">
@@ -1225,7 +1188,6 @@
       <c r="H34" s="9" t="n"/>
       <c r="I34" s="9" t="n"/>
       <c r="J34" s="9" t="n"/>
-      <c r="K34" s="9" t="n"/>
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="6" t="n">
@@ -1240,7 +1202,6 @@
       <c r="H35" s="7" t="n"/>
       <c r="I35" s="7" t="n"/>
       <c r="J35" s="7" t="n"/>
-      <c r="K35" s="7" t="n"/>
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="8" t="n">
@@ -1255,7 +1216,6 @@
       <c r="H36" s="9" t="n"/>
       <c r="I36" s="9" t="n"/>
       <c r="J36" s="9" t="n"/>
-      <c r="K36" s="9" t="n"/>
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="6" t="n">
@@ -1270,7 +1230,6 @@
       <c r="H37" s="7" t="n"/>
       <c r="I37" s="7" t="n"/>
       <c r="J37" s="7" t="n"/>
-      <c r="K37" s="7" t="n"/>
     </row>
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="8" t="n">
@@ -1285,7 +1244,6 @@
       <c r="H38" s="9" t="n"/>
       <c r="I38" s="9" t="n"/>
       <c r="J38" s="9" t="n"/>
-      <c r="K38" s="9" t="n"/>
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="6" t="n">
@@ -1300,7 +1258,6 @@
       <c r="H39" s="7" t="n"/>
       <c r="I39" s="7" t="n"/>
       <c r="J39" s="7" t="n"/>
-      <c r="K39" s="7" t="n"/>
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="8" t="n">
@@ -1315,7 +1272,6 @@
       <c r="H40" s="9" t="n"/>
       <c r="I40" s="9" t="n"/>
       <c r="J40" s="9" t="n"/>
-      <c r="K40" s="9" t="n"/>
     </row>
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="6" t="n">
@@ -1330,7 +1286,6 @@
       <c r="H41" s="7" t="n"/>
       <c r="I41" s="7" t="n"/>
       <c r="J41" s="7" t="n"/>
-      <c r="K41" s="7" t="n"/>
     </row>
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="8" t="n">
@@ -1345,7 +1300,6 @@
       <c r="H42" s="9" t="n"/>
       <c r="I42" s="9" t="n"/>
       <c r="J42" s="9" t="n"/>
-      <c r="K42" s="9" t="n"/>
     </row>
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="6" t="n">
@@ -1360,7 +1314,6 @@
       <c r="H43" s="7" t="n"/>
       <c r="I43" s="7" t="n"/>
       <c r="J43" s="7" t="n"/>
-      <c r="K43" s="7" t="n"/>
     </row>
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="8" t="n">
@@ -1375,7 +1328,6 @@
       <c r="H44" s="9" t="n"/>
       <c r="I44" s="9" t="n"/>
       <c r="J44" s="9" t="n"/>
-      <c r="K44" s="9" t="n"/>
     </row>
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="6" t="n">
@@ -1390,7 +1342,6 @@
       <c r="H45" s="7" t="n"/>
       <c r="I45" s="7" t="n"/>
       <c r="J45" s="7" t="n"/>
-      <c r="K45" s="7" t="n"/>
     </row>
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="8" t="n">
@@ -1405,7 +1356,6 @@
       <c r="H46" s="9" t="n"/>
       <c r="I46" s="9" t="n"/>
       <c r="J46" s="9" t="n"/>
-      <c r="K46" s="9" t="n"/>
     </row>
     <row r="47" ht="19" customHeight="1">
       <c r="A47" s="6" t="n">
@@ -1420,7 +1370,6 @@
       <c r="H47" s="7" t="n"/>
       <c r="I47" s="7" t="n"/>
       <c r="J47" s="7" t="n"/>
-      <c r="K47" s="7" t="n"/>
     </row>
     <row r="48" ht="19" customHeight="1">
       <c r="A48" s="8" t="n">
@@ -1435,7 +1384,6 @@
       <c r="H48" s="9" t="n"/>
       <c r="I48" s="9" t="n"/>
       <c r="J48" s="9" t="n"/>
-      <c r="K48" s="9" t="n"/>
     </row>
     <row r="49" ht="19" customHeight="1">
       <c r="A49" s="6" t="n">
@@ -1450,7 +1398,6 @@
       <c r="H49" s="7" t="n"/>
       <c r="I49" s="7" t="n"/>
       <c r="J49" s="7" t="n"/>
-      <c r="K49" s="7" t="n"/>
     </row>
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="8" t="n">
@@ -1465,7 +1412,6 @@
       <c r="H50" s="9" t="n"/>
       <c r="I50" s="9" t="n"/>
       <c r="J50" s="9" t="n"/>
-      <c r="K50" s="9" t="n"/>
     </row>
     <row r="51" ht="19" customHeight="1">
       <c r="A51" s="6" t="n">
@@ -1480,7 +1426,6 @@
       <c r="H51" s="7" t="n"/>
       <c r="I51" s="7" t="n"/>
       <c r="J51" s="7" t="n"/>
-      <c r="K51" s="7" t="n"/>
     </row>
     <row r="52" ht="19" customHeight="1">
       <c r="A52" s="8" t="n">
@@ -1495,7 +1440,6 @@
       <c r="H52" s="9" t="n"/>
       <c r="I52" s="9" t="n"/>
       <c r="J52" s="9" t="n"/>
-      <c r="K52" s="9" t="n"/>
     </row>
     <row r="53" ht="19" customHeight="1">
       <c r="A53" s="6" t="n">
@@ -1510,7 +1454,6 @@
       <c r="H53" s="7" t="n"/>
       <c r="I53" s="7" t="n"/>
       <c r="J53" s="7" t="n"/>
-      <c r="K53" s="7" t="n"/>
     </row>
     <row r="54" ht="19" customHeight="1">
       <c r="A54" s="8" t="n">
@@ -1525,7 +1468,6 @@
       <c r="H54" s="9" t="n"/>
       <c r="I54" s="9" t="n"/>
       <c r="J54" s="9" t="n"/>
-      <c r="K54" s="9" t="n"/>
     </row>
     <row r="55" ht="19" customHeight="1">
       <c r="A55" s="6" t="n">
@@ -1540,7 +1482,6 @@
       <c r="H55" s="7" t="n"/>
       <c r="I55" s="7" t="n"/>
       <c r="J55" s="7" t="n"/>
-      <c r="K55" s="7" t="n"/>
     </row>
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="8" t="n">
@@ -1555,7 +1496,6 @@
       <c r="H56" s="9" t="n"/>
       <c r="I56" s="9" t="n"/>
       <c r="J56" s="9" t="n"/>
-      <c r="K56" s="9" t="n"/>
     </row>
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="6" t="n">
@@ -1570,7 +1510,6 @@
       <c r="H57" s="7" t="n"/>
       <c r="I57" s="7" t="n"/>
       <c r="J57" s="7" t="n"/>
-      <c r="K57" s="7" t="n"/>
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="8" t="n">
@@ -1585,7 +1524,6 @@
       <c r="H58" s="9" t="n"/>
       <c r="I58" s="9" t="n"/>
       <c r="J58" s="9" t="n"/>
-      <c r="K58" s="9" t="n"/>
     </row>
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="6" t="n">
@@ -1600,7 +1538,6 @@
       <c r="H59" s="7" t="n"/>
       <c r="I59" s="7" t="n"/>
       <c r="J59" s="7" t="n"/>
-      <c r="K59" s="7" t="n"/>
     </row>
     <row r="60" ht="19" customHeight="1">
       <c r="A60" s="8" t="n">
@@ -1615,7 +1552,6 @@
       <c r="H60" s="9" t="n"/>
       <c r="I60" s="9" t="n"/>
       <c r="J60" s="9" t="n"/>
-      <c r="K60" s="9" t="n"/>
     </row>
     <row r="61" ht="19" customHeight="1">
       <c r="A61" s="6" t="n">
@@ -1630,7 +1566,6 @@
       <c r="H61" s="7" t="n"/>
       <c r="I61" s="7" t="n"/>
       <c r="J61" s="7" t="n"/>
-      <c r="K61" s="7" t="n"/>
     </row>
     <row r="62" ht="19" customHeight="1">
       <c r="A62" s="8" t="n">
@@ -1645,7 +1580,6 @@
       <c r="H62" s="9" t="n"/>
       <c r="I62" s="9" t="n"/>
       <c r="J62" s="9" t="n"/>
-      <c r="K62" s="9" t="n"/>
     </row>
     <row r="63" ht="19" customHeight="1">
       <c r="A63" s="6" t="n">
@@ -1660,7 +1594,6 @@
       <c r="H63" s="7" t="n"/>
       <c r="I63" s="7" t="n"/>
       <c r="J63" s="7" t="n"/>
-      <c r="K63" s="7" t="n"/>
     </row>
     <row r="64" ht="19" customHeight="1">
       <c r="A64" s="8" t="n">
@@ -1675,7 +1608,6 @@
       <c r="H64" s="9" t="n"/>
       <c r="I64" s="9" t="n"/>
       <c r="J64" s="9" t="n"/>
-      <c r="K64" s="9" t="n"/>
     </row>
     <row r="65" ht="19" customHeight="1">
       <c r="A65" s="6" t="n">
@@ -1690,7 +1622,6 @@
       <c r="H65" s="7" t="n"/>
       <c r="I65" s="7" t="n"/>
       <c r="J65" s="7" t="n"/>
-      <c r="K65" s="7" t="n"/>
     </row>
     <row r="66" ht="19" customHeight="1">
       <c r="A66" s="8" t="n">
@@ -1705,7 +1636,6 @@
       <c r="H66" s="9" t="n"/>
       <c r="I66" s="9" t="n"/>
       <c r="J66" s="9" t="n"/>
-      <c r="K66" s="9" t="n"/>
     </row>
     <row r="67" ht="19" customHeight="1">
       <c r="A67" s="6" t="n">
@@ -1720,7 +1650,6 @@
       <c r="H67" s="7" t="n"/>
       <c r="I67" s="7" t="n"/>
       <c r="J67" s="7" t="n"/>
-      <c r="K67" s="7" t="n"/>
     </row>
     <row r="68" ht="19" customHeight="1">
       <c r="A68" s="8" t="n">
@@ -1735,7 +1664,6 @@
       <c r="H68" s="9" t="n"/>
       <c r="I68" s="9" t="n"/>
       <c r="J68" s="9" t="n"/>
-      <c r="K68" s="9" t="n"/>
     </row>
     <row r="69" ht="19" customHeight="1">
       <c r="A69" s="6" t="n">
@@ -1750,7 +1678,6 @@
       <c r="H69" s="7" t="n"/>
       <c r="I69" s="7" t="n"/>
       <c r="J69" s="7" t="n"/>
-      <c r="K69" s="7" t="n"/>
     </row>
     <row r="70" ht="19" customHeight="1">
       <c r="A70" s="8" t="n">
@@ -1765,7 +1692,6 @@
       <c r="H70" s="9" t="n"/>
       <c r="I70" s="9" t="n"/>
       <c r="J70" s="9" t="n"/>
-      <c r="K70" s="9" t="n"/>
     </row>
     <row r="71" ht="19" customHeight="1">
       <c r="A71" s="6" t="n">
@@ -1780,7 +1706,6 @@
       <c r="H71" s="7" t="n"/>
       <c r="I71" s="7" t="n"/>
       <c r="J71" s="7" t="n"/>
-      <c r="K71" s="7" t="n"/>
     </row>
     <row r="72" ht="19" customHeight="1">
       <c r="A72" s="8" t="n">
@@ -1795,7 +1720,6 @@
       <c r="H72" s="9" t="n"/>
       <c r="I72" s="9" t="n"/>
       <c r="J72" s="9" t="n"/>
-      <c r="K72" s="9" t="n"/>
     </row>
     <row r="73" ht="19" customHeight="1">
       <c r="A73" s="6" t="n">
@@ -1810,7 +1734,6 @@
       <c r="H73" s="7" t="n"/>
       <c r="I73" s="7" t="n"/>
       <c r="J73" s="7" t="n"/>
-      <c r="K73" s="7" t="n"/>
     </row>
     <row r="74" ht="19" customHeight="1">
       <c r="A74" s="8" t="n">
@@ -1825,7 +1748,6 @@
       <c r="H74" s="9" t="n"/>
       <c r="I74" s="9" t="n"/>
       <c r="J74" s="9" t="n"/>
-      <c r="K74" s="9" t="n"/>
     </row>
     <row r="75" ht="19" customHeight="1">
       <c r="A75" s="6" t="n">
@@ -1840,7 +1762,6 @@
       <c r="H75" s="7" t="n"/>
       <c r="I75" s="7" t="n"/>
       <c r="J75" s="7" t="n"/>
-      <c r="K75" s="7" t="n"/>
     </row>
     <row r="76" ht="19" customHeight="1">
       <c r="A76" s="8" t="n">
@@ -1855,7 +1776,6 @@
       <c r="H76" s="9" t="n"/>
       <c r="I76" s="9" t="n"/>
       <c r="J76" s="9" t="n"/>
-      <c r="K76" s="9" t="n"/>
     </row>
     <row r="77" ht="19" customHeight="1">
       <c r="A77" s="6" t="n">
@@ -1870,7 +1790,6 @@
       <c r="H77" s="7" t="n"/>
       <c r="I77" s="7" t="n"/>
       <c r="J77" s="7" t="n"/>
-      <c r="K77" s="7" t="n"/>
     </row>
     <row r="78" ht="19" customHeight="1">
       <c r="A78" s="8" t="n">
@@ -1885,7 +1804,6 @@
       <c r="H78" s="9" t="n"/>
       <c r="I78" s="9" t="n"/>
       <c r="J78" s="9" t="n"/>
-      <c r="K78" s="9" t="n"/>
     </row>
     <row r="79" ht="19" customHeight="1">
       <c r="A79" s="6" t="n">
@@ -1900,7 +1818,6 @@
       <c r="H79" s="7" t="n"/>
       <c r="I79" s="7" t="n"/>
       <c r="J79" s="7" t="n"/>
-      <c r="K79" s="7" t="n"/>
     </row>
     <row r="80" ht="19" customHeight="1">
       <c r="A80" s="8" t="n">
@@ -1915,7 +1832,6 @@
       <c r="H80" s="9" t="n"/>
       <c r="I80" s="9" t="n"/>
       <c r="J80" s="9" t="n"/>
-      <c r="K80" s="9" t="n"/>
     </row>
     <row r="81" ht="19" customHeight="1">
       <c r="A81" s="6" t="n">
@@ -1930,7 +1846,6 @@
       <c r="H81" s="7" t="n"/>
       <c r="I81" s="7" t="n"/>
       <c r="J81" s="7" t="n"/>
-      <c r="K81" s="7" t="n"/>
     </row>
     <row r="82" ht="19" customHeight="1">
       <c r="A82" s="8" t="n">
@@ -1945,7 +1860,6 @@
       <c r="H82" s="9" t="n"/>
       <c r="I82" s="9" t="n"/>
       <c r="J82" s="9" t="n"/>
-      <c r="K82" s="9" t="n"/>
     </row>
     <row r="83" ht="19" customHeight="1">
       <c r="A83" s="6" t="n">
@@ -1960,7 +1874,6 @@
       <c r="H83" s="7" t="n"/>
       <c r="I83" s="7" t="n"/>
       <c r="J83" s="7" t="n"/>
-      <c r="K83" s="7" t="n"/>
     </row>
     <row r="84" ht="19" customHeight="1">
       <c r="A84" s="8" t="n">
@@ -1975,7 +1888,6 @@
       <c r="H84" s="9" t="n"/>
       <c r="I84" s="9" t="n"/>
       <c r="J84" s="9" t="n"/>
-      <c r="K84" s="9" t="n"/>
     </row>
     <row r="85" ht="19" customHeight="1">
       <c r="A85" s="6" t="n">
@@ -1990,7 +1902,6 @@
       <c r="H85" s="7" t="n"/>
       <c r="I85" s="7" t="n"/>
       <c r="J85" s="7" t="n"/>
-      <c r="K85" s="7" t="n"/>
     </row>
     <row r="86" ht="19" customHeight="1">
       <c r="A86" s="8" t="n">
@@ -2005,7 +1916,6 @@
       <c r="H86" s="9" t="n"/>
       <c r="I86" s="9" t="n"/>
       <c r="J86" s="9" t="n"/>
-      <c r="K86" s="9" t="n"/>
     </row>
     <row r="87" ht="19" customHeight="1">
       <c r="A87" s="6" t="n">
@@ -2020,7 +1930,6 @@
       <c r="H87" s="7" t="n"/>
       <c r="I87" s="7" t="n"/>
       <c r="J87" s="7" t="n"/>
-      <c r="K87" s="7" t="n"/>
     </row>
     <row r="88" ht="19" customHeight="1">
       <c r="A88" s="8" t="n">
@@ -2035,7 +1944,6 @@
       <c r="H88" s="9" t="n"/>
       <c r="I88" s="9" t="n"/>
       <c r="J88" s="9" t="n"/>
-      <c r="K88" s="9" t="n"/>
     </row>
     <row r="89" ht="19" customHeight="1">
       <c r="A89" s="6" t="n">
@@ -2050,7 +1958,6 @@
       <c r="H89" s="7" t="n"/>
       <c r="I89" s="7" t="n"/>
       <c r="J89" s="7" t="n"/>
-      <c r="K89" s="7" t="n"/>
     </row>
     <row r="90" ht="19" customHeight="1">
       <c r="A90" s="8" t="n">
@@ -2065,7 +1972,6 @@
       <c r="H90" s="9" t="n"/>
       <c r="I90" s="9" t="n"/>
       <c r="J90" s="9" t="n"/>
-      <c r="K90" s="9" t="n"/>
     </row>
     <row r="91" ht="19" customHeight="1">
       <c r="A91" s="6" t="n">
@@ -2080,7 +1986,6 @@
       <c r="H91" s="7" t="n"/>
       <c r="I91" s="7" t="n"/>
       <c r="J91" s="7" t="n"/>
-      <c r="K91" s="7" t="n"/>
     </row>
     <row r="92" ht="19" customHeight="1">
       <c r="A92" s="8" t="n">
@@ -2095,17 +2000,1556 @@
       <c r="H92" s="9" t="n"/>
       <c r="I92" s="9" t="n"/>
       <c r="J92" s="9" t="n"/>
-      <c r="K92" s="9" t="n"/>
+    </row>
+    <row r="93" ht="19" customHeight="1">
+      <c r="A93" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="7" t="n"/>
+      <c r="C93" s="7" t="n"/>
+      <c r="D93" s="7" t="n"/>
+      <c r="E93" s="7" t="n"/>
+      <c r="F93" s="7" t="n"/>
+      <c r="G93" s="7" t="n"/>
+      <c r="H93" s="7" t="n"/>
+      <c r="I93" s="7" t="n"/>
+      <c r="J93" s="7" t="n"/>
+    </row>
+    <row r="94" ht="19" customHeight="1">
+      <c r="A94" s="8" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="9" t="n"/>
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="9" t="n"/>
+      <c r="E94" s="9" t="n"/>
+      <c r="F94" s="9" t="n"/>
+      <c r="G94" s="9" t="n"/>
+      <c r="H94" s="9" t="n"/>
+      <c r="I94" s="9" t="n"/>
+      <c r="J94" s="9" t="n"/>
+    </row>
+    <row r="95" ht="19" customHeight="1">
+      <c r="A95" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="7" t="n"/>
+      <c r="C95" s="7" t="n"/>
+      <c r="D95" s="7" t="n"/>
+      <c r="E95" s="7" t="n"/>
+      <c r="F95" s="7" t="n"/>
+      <c r="G95" s="7" t="n"/>
+      <c r="H95" s="7" t="n"/>
+      <c r="I95" s="7" t="n"/>
+      <c r="J95" s="7" t="n"/>
+    </row>
+    <row r="96" ht="19" customHeight="1">
+      <c r="A96" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="9" t="n"/>
+      <c r="C96" s="9" t="n"/>
+      <c r="D96" s="9" t="n"/>
+      <c r="E96" s="9" t="n"/>
+      <c r="F96" s="9" t="n"/>
+      <c r="G96" s="9" t="n"/>
+      <c r="H96" s="9" t="n"/>
+      <c r="I96" s="9" t="n"/>
+      <c r="J96" s="9" t="n"/>
+    </row>
+    <row r="97" ht="19" customHeight="1">
+      <c r="A97" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="7" t="n"/>
+      <c r="C97" s="7" t="n"/>
+      <c r="D97" s="7" t="n"/>
+      <c r="E97" s="7" t="n"/>
+      <c r="F97" s="7" t="n"/>
+      <c r="G97" s="7" t="n"/>
+      <c r="H97" s="7" t="n"/>
+      <c r="I97" s="7" t="n"/>
+      <c r="J97" s="7" t="n"/>
+    </row>
+    <row r="98" ht="19" customHeight="1">
+      <c r="A98" s="8" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="9" t="n"/>
+      <c r="C98" s="9" t="n"/>
+      <c r="D98" s="9" t="n"/>
+      <c r="E98" s="9" t="n"/>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="9" t="n"/>
+      <c r="H98" s="9" t="n"/>
+      <c r="I98" s="9" t="n"/>
+      <c r="J98" s="9" t="n"/>
+    </row>
+    <row r="99" ht="19" customHeight="1">
+      <c r="A99" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="7" t="n"/>
+      <c r="C99" s="7" t="n"/>
+      <c r="D99" s="7" t="n"/>
+      <c r="E99" s="7" t="n"/>
+      <c r="F99" s="7" t="n"/>
+      <c r="G99" s="7" t="n"/>
+      <c r="H99" s="7" t="n"/>
+      <c r="I99" s="7" t="n"/>
+      <c r="J99" s="7" t="n"/>
+    </row>
+    <row r="100" ht="19" customHeight="1">
+      <c r="A100" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="9" t="n"/>
+      <c r="C100" s="9" t="n"/>
+      <c r="D100" s="9" t="n"/>
+      <c r="E100" s="9" t="n"/>
+      <c r="F100" s="9" t="n"/>
+      <c r="G100" s="9" t="n"/>
+      <c r="H100" s="9" t="n"/>
+      <c r="I100" s="9" t="n"/>
+      <c r="J100" s="9" t="n"/>
+    </row>
+    <row r="101" ht="19" customHeight="1">
+      <c r="A101" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="7" t="n"/>
+      <c r="C101" s="7" t="n"/>
+      <c r="D101" s="7" t="n"/>
+      <c r="E101" s="7" t="n"/>
+      <c r="F101" s="7" t="n"/>
+      <c r="G101" s="7" t="n"/>
+      <c r="H101" s="7" t="n"/>
+      <c r="I101" s="7" t="n"/>
+      <c r="J101" s="7" t="n"/>
+    </row>
+    <row r="102" ht="19" customHeight="1">
+      <c r="A102" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="9" t="n"/>
+      <c r="C102" s="9" t="n"/>
+      <c r="D102" s="9" t="n"/>
+      <c r="E102" s="9" t="n"/>
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="9" t="n"/>
+      <c r="H102" s="9" t="n"/>
+      <c r="I102" s="9" t="n"/>
+      <c r="J102" s="9" t="n"/>
+    </row>
+    <row r="103" ht="19" customHeight="1">
+      <c r="A103" s="6" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="7" t="n"/>
+      <c r="C103" s="7" t="n"/>
+      <c r="D103" s="7" t="n"/>
+      <c r="E103" s="7" t="n"/>
+      <c r="F103" s="7" t="n"/>
+      <c r="G103" s="7" t="n"/>
+      <c r="H103" s="7" t="n"/>
+      <c r="I103" s="7" t="n"/>
+      <c r="J103" s="7" t="n"/>
+    </row>
+    <row r="104" ht="19" customHeight="1">
+      <c r="A104" s="8" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="9" t="n"/>
+      <c r="C104" s="9" t="n"/>
+      <c r="D104" s="9" t="n"/>
+      <c r="E104" s="9" t="n"/>
+      <c r="F104" s="9" t="n"/>
+      <c r="G104" s="9" t="n"/>
+      <c r="H104" s="9" t="n"/>
+      <c r="I104" s="9" t="n"/>
+      <c r="J104" s="9" t="n"/>
+    </row>
+    <row r="105" ht="19" customHeight="1">
+      <c r="A105" s="6" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="7" t="n"/>
+      <c r="C105" s="7" t="n"/>
+      <c r="D105" s="7" t="n"/>
+      <c r="E105" s="7" t="n"/>
+      <c r="F105" s="7" t="n"/>
+      <c r="G105" s="7" t="n"/>
+      <c r="H105" s="7" t="n"/>
+      <c r="I105" s="7" t="n"/>
+      <c r="J105" s="7" t="n"/>
+    </row>
+    <row r="106" ht="19" customHeight="1">
+      <c r="A106" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="9" t="n"/>
+      <c r="C106" s="9" t="n"/>
+      <c r="D106" s="9" t="n"/>
+      <c r="E106" s="9" t="n"/>
+      <c r="F106" s="9" t="n"/>
+      <c r="G106" s="9" t="n"/>
+      <c r="H106" s="9" t="n"/>
+      <c r="I106" s="9" t="n"/>
+      <c r="J106" s="9" t="n"/>
+    </row>
+    <row r="107" ht="19" customHeight="1">
+      <c r="A107" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="7" t="n"/>
+      <c r="C107" s="7" t="n"/>
+      <c r="D107" s="7" t="n"/>
+      <c r="E107" s="7" t="n"/>
+      <c r="F107" s="7" t="n"/>
+      <c r="G107" s="7" t="n"/>
+      <c r="H107" s="7" t="n"/>
+      <c r="I107" s="7" t="n"/>
+      <c r="J107" s="7" t="n"/>
+    </row>
+    <row r="108" ht="19" customHeight="1">
+      <c r="A108" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="9" t="n"/>
+      <c r="C108" s="9" t="n"/>
+      <c r="D108" s="9" t="n"/>
+      <c r="E108" s="9" t="n"/>
+      <c r="F108" s="9" t="n"/>
+      <c r="G108" s="9" t="n"/>
+      <c r="H108" s="9" t="n"/>
+      <c r="I108" s="9" t="n"/>
+      <c r="J108" s="9" t="n"/>
+    </row>
+    <row r="109" ht="19" customHeight="1">
+      <c r="A109" s="6" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="7" t="n"/>
+      <c r="C109" s="7" t="n"/>
+      <c r="D109" s="7" t="n"/>
+      <c r="E109" s="7" t="n"/>
+      <c r="F109" s="7" t="n"/>
+      <c r="G109" s="7" t="n"/>
+      <c r="H109" s="7" t="n"/>
+      <c r="I109" s="7" t="n"/>
+      <c r="J109" s="7" t="n"/>
+    </row>
+    <row r="110" ht="19" customHeight="1">
+      <c r="A110" s="8" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="9" t="n"/>
+      <c r="C110" s="9" t="n"/>
+      <c r="D110" s="9" t="n"/>
+      <c r="E110" s="9" t="n"/>
+      <c r="F110" s="9" t="n"/>
+      <c r="G110" s="9" t="n"/>
+      <c r="H110" s="9" t="n"/>
+      <c r="I110" s="9" t="n"/>
+      <c r="J110" s="9" t="n"/>
+    </row>
+    <row r="111" ht="19" customHeight="1">
+      <c r="A111" s="6" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="7" t="n"/>
+      <c r="C111" s="7" t="n"/>
+      <c r="D111" s="7" t="n"/>
+      <c r="E111" s="7" t="n"/>
+      <c r="F111" s="7" t="n"/>
+      <c r="G111" s="7" t="n"/>
+      <c r="H111" s="7" t="n"/>
+      <c r="I111" s="7" t="n"/>
+      <c r="J111" s="7" t="n"/>
+    </row>
+    <row r="112" ht="19" customHeight="1">
+      <c r="A112" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="9" t="n"/>
+      <c r="C112" s="9" t="n"/>
+      <c r="D112" s="9" t="n"/>
+      <c r="E112" s="9" t="n"/>
+      <c r="F112" s="9" t="n"/>
+      <c r="G112" s="9" t="n"/>
+      <c r="H112" s="9" t="n"/>
+      <c r="I112" s="9" t="n"/>
+      <c r="J112" s="9" t="n"/>
+    </row>
+    <row r="113" ht="19" customHeight="1">
+      <c r="A113" s="6" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="7" t="n"/>
+      <c r="C113" s="7" t="n"/>
+      <c r="D113" s="7" t="n"/>
+      <c r="E113" s="7" t="n"/>
+      <c r="F113" s="7" t="n"/>
+      <c r="G113" s="7" t="n"/>
+      <c r="H113" s="7" t="n"/>
+      <c r="I113" s="7" t="n"/>
+      <c r="J113" s="7" t="n"/>
+    </row>
+    <row r="114" ht="19" customHeight="1">
+      <c r="A114" s="8" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="9" t="n"/>
+      <c r="C114" s="9" t="n"/>
+      <c r="D114" s="9" t="n"/>
+      <c r="E114" s="9" t="n"/>
+      <c r="F114" s="9" t="n"/>
+      <c r="G114" s="9" t="n"/>
+      <c r="H114" s="9" t="n"/>
+      <c r="I114" s="9" t="n"/>
+      <c r="J114" s="9" t="n"/>
+    </row>
+    <row r="115" ht="19" customHeight="1">
+      <c r="A115" s="6" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="7" t="n"/>
+      <c r="C115" s="7" t="n"/>
+      <c r="D115" s="7" t="n"/>
+      <c r="E115" s="7" t="n"/>
+      <c r="F115" s="7" t="n"/>
+      <c r="G115" s="7" t="n"/>
+      <c r="H115" s="7" t="n"/>
+      <c r="I115" s="7" t="n"/>
+      <c r="J115" s="7" t="n"/>
+    </row>
+    <row r="116" ht="19" customHeight="1">
+      <c r="A116" s="8" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="9" t="n"/>
+      <c r="C116" s="9" t="n"/>
+      <c r="D116" s="9" t="n"/>
+      <c r="E116" s="9" t="n"/>
+      <c r="F116" s="9" t="n"/>
+      <c r="G116" s="9" t="n"/>
+      <c r="H116" s="9" t="n"/>
+      <c r="I116" s="9" t="n"/>
+      <c r="J116" s="9" t="n"/>
+    </row>
+    <row r="117" ht="19" customHeight="1">
+      <c r="A117" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="7" t="n"/>
+      <c r="C117" s="7" t="n"/>
+      <c r="D117" s="7" t="n"/>
+      <c r="E117" s="7" t="n"/>
+      <c r="F117" s="7" t="n"/>
+      <c r="G117" s="7" t="n"/>
+      <c r="H117" s="7" t="n"/>
+      <c r="I117" s="7" t="n"/>
+      <c r="J117" s="7" t="n"/>
+    </row>
+    <row r="118" ht="19" customHeight="1">
+      <c r="A118" s="8" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="9" t="n"/>
+      <c r="C118" s="9" t="n"/>
+      <c r="D118" s="9" t="n"/>
+      <c r="E118" s="9" t="n"/>
+      <c r="F118" s="9" t="n"/>
+      <c r="G118" s="9" t="n"/>
+      <c r="H118" s="9" t="n"/>
+      <c r="I118" s="9" t="n"/>
+      <c r="J118" s="9" t="n"/>
+    </row>
+    <row r="119" ht="19" customHeight="1">
+      <c r="A119" s="6" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="7" t="n"/>
+      <c r="C119" s="7" t="n"/>
+      <c r="D119" s="7" t="n"/>
+      <c r="E119" s="7" t="n"/>
+      <c r="F119" s="7" t="n"/>
+      <c r="G119" s="7" t="n"/>
+      <c r="H119" s="7" t="n"/>
+      <c r="I119" s="7" t="n"/>
+      <c r="J119" s="7" t="n"/>
+    </row>
+    <row r="120" ht="19" customHeight="1">
+      <c r="A120" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="9" t="n"/>
+      <c r="C120" s="9" t="n"/>
+      <c r="D120" s="9" t="n"/>
+      <c r="E120" s="9" t="n"/>
+      <c r="F120" s="9" t="n"/>
+      <c r="G120" s="9" t="n"/>
+      <c r="H120" s="9" t="n"/>
+      <c r="I120" s="9" t="n"/>
+      <c r="J120" s="9" t="n"/>
+    </row>
+    <row r="121" ht="19" customHeight="1">
+      <c r="A121" s="6" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="7" t="n"/>
+      <c r="C121" s="7" t="n"/>
+      <c r="D121" s="7" t="n"/>
+      <c r="E121" s="7" t="n"/>
+      <c r="F121" s="7" t="n"/>
+      <c r="G121" s="7" t="n"/>
+      <c r="H121" s="7" t="n"/>
+      <c r="I121" s="7" t="n"/>
+      <c r="J121" s="7" t="n"/>
+    </row>
+    <row r="122" ht="19" customHeight="1">
+      <c r="A122" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="9" t="n"/>
+      <c r="C122" s="9" t="n"/>
+      <c r="D122" s="9" t="n"/>
+      <c r="E122" s="9" t="n"/>
+      <c r="F122" s="9" t="n"/>
+      <c r="G122" s="9" t="n"/>
+      <c r="H122" s="9" t="n"/>
+      <c r="I122" s="9" t="n"/>
+      <c r="J122" s="9" t="n"/>
+    </row>
+    <row r="123" ht="19" customHeight="1">
+      <c r="A123" s="6" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="7" t="n"/>
+      <c r="C123" s="7" t="n"/>
+      <c r="D123" s="7" t="n"/>
+      <c r="E123" s="7" t="n"/>
+      <c r="F123" s="7" t="n"/>
+      <c r="G123" s="7" t="n"/>
+      <c r="H123" s="7" t="n"/>
+      <c r="I123" s="7" t="n"/>
+      <c r="J123" s="7" t="n"/>
+    </row>
+    <row r="124" ht="19" customHeight="1">
+      <c r="A124" s="8" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="9" t="n"/>
+      <c r="C124" s="9" t="n"/>
+      <c r="D124" s="9" t="n"/>
+      <c r="E124" s="9" t="n"/>
+      <c r="F124" s="9" t="n"/>
+      <c r="G124" s="9" t="n"/>
+      <c r="H124" s="9" t="n"/>
+      <c r="I124" s="9" t="n"/>
+      <c r="J124" s="9" t="n"/>
+    </row>
+    <row r="125" ht="19" customHeight="1">
+      <c r="A125" s="6" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="7" t="n"/>
+      <c r="C125" s="7" t="n"/>
+      <c r="D125" s="7" t="n"/>
+      <c r="E125" s="7" t="n"/>
+      <c r="F125" s="7" t="n"/>
+      <c r="G125" s="7" t="n"/>
+      <c r="H125" s="7" t="n"/>
+      <c r="I125" s="7" t="n"/>
+      <c r="J125" s="7" t="n"/>
+    </row>
+    <row r="126" ht="19" customHeight="1">
+      <c r="A126" s="8" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="9" t="n"/>
+      <c r="C126" s="9" t="n"/>
+      <c r="D126" s="9" t="n"/>
+      <c r="E126" s="9" t="n"/>
+      <c r="F126" s="9" t="n"/>
+      <c r="G126" s="9" t="n"/>
+      <c r="H126" s="9" t="n"/>
+      <c r="I126" s="9" t="n"/>
+      <c r="J126" s="9" t="n"/>
+    </row>
+    <row r="127" ht="19" customHeight="1">
+      <c r="A127" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="7" t="n"/>
+      <c r="C127" s="7" t="n"/>
+      <c r="D127" s="7" t="n"/>
+      <c r="E127" s="7" t="n"/>
+      <c r="F127" s="7" t="n"/>
+      <c r="G127" s="7" t="n"/>
+      <c r="H127" s="7" t="n"/>
+      <c r="I127" s="7" t="n"/>
+      <c r="J127" s="7" t="n"/>
+    </row>
+    <row r="128" ht="19" customHeight="1">
+      <c r="A128" s="8" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="9" t="n"/>
+      <c r="C128" s="9" t="n"/>
+      <c r="D128" s="9" t="n"/>
+      <c r="E128" s="9" t="n"/>
+      <c r="F128" s="9" t="n"/>
+      <c r="G128" s="9" t="n"/>
+      <c r="H128" s="9" t="n"/>
+      <c r="I128" s="9" t="n"/>
+      <c r="J128" s="9" t="n"/>
+    </row>
+    <row r="129" ht="19" customHeight="1">
+      <c r="A129" s="6" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="7" t="n"/>
+      <c r="C129" s="7" t="n"/>
+      <c r="D129" s="7" t="n"/>
+      <c r="E129" s="7" t="n"/>
+      <c r="F129" s="7" t="n"/>
+      <c r="G129" s="7" t="n"/>
+      <c r="H129" s="7" t="n"/>
+      <c r="I129" s="7" t="n"/>
+      <c r="J129" s="7" t="n"/>
+    </row>
+    <row r="130" ht="19" customHeight="1">
+      <c r="A130" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="9" t="n"/>
+      <c r="C130" s="9" t="n"/>
+      <c r="D130" s="9" t="n"/>
+      <c r="E130" s="9" t="n"/>
+      <c r="F130" s="9" t="n"/>
+      <c r="G130" s="9" t="n"/>
+      <c r="H130" s="9" t="n"/>
+      <c r="I130" s="9" t="n"/>
+      <c r="J130" s="9" t="n"/>
+    </row>
+    <row r="131" ht="19" customHeight="1">
+      <c r="A131" s="6" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="7" t="n"/>
+      <c r="C131" s="7" t="n"/>
+      <c r="D131" s="7" t="n"/>
+      <c r="E131" s="7" t="n"/>
+      <c r="F131" s="7" t="n"/>
+      <c r="G131" s="7" t="n"/>
+      <c r="H131" s="7" t="n"/>
+      <c r="I131" s="7" t="n"/>
+      <c r="J131" s="7" t="n"/>
+    </row>
+    <row r="132" ht="19" customHeight="1">
+      <c r="A132" s="8" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="9" t="n"/>
+      <c r="C132" s="9" t="n"/>
+      <c r="D132" s="9" t="n"/>
+      <c r="E132" s="9" t="n"/>
+      <c r="F132" s="9" t="n"/>
+      <c r="G132" s="9" t="n"/>
+      <c r="H132" s="9" t="n"/>
+      <c r="I132" s="9" t="n"/>
+      <c r="J132" s="9" t="n"/>
+    </row>
+    <row r="133" ht="19" customHeight="1">
+      <c r="A133" s="6" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="7" t="n"/>
+      <c r="C133" s="7" t="n"/>
+      <c r="D133" s="7" t="n"/>
+      <c r="E133" s="7" t="n"/>
+      <c r="F133" s="7" t="n"/>
+      <c r="G133" s="7" t="n"/>
+      <c r="H133" s="7" t="n"/>
+      <c r="I133" s="7" t="n"/>
+      <c r="J133" s="7" t="n"/>
+    </row>
+    <row r="134" ht="19" customHeight="1">
+      <c r="A134" s="8" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" s="9" t="n"/>
+      <c r="C134" s="9" t="n"/>
+      <c r="D134" s="9" t="n"/>
+      <c r="E134" s="9" t="n"/>
+      <c r="F134" s="9" t="n"/>
+      <c r="G134" s="9" t="n"/>
+      <c r="H134" s="9" t="n"/>
+      <c r="I134" s="9" t="n"/>
+      <c r="J134" s="9" t="n"/>
+    </row>
+    <row r="135" ht="19" customHeight="1">
+      <c r="A135" s="6" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" s="7" t="n"/>
+      <c r="C135" s="7" t="n"/>
+      <c r="D135" s="7" t="n"/>
+      <c r="E135" s="7" t="n"/>
+      <c r="F135" s="7" t="n"/>
+      <c r="G135" s="7" t="n"/>
+      <c r="H135" s="7" t="n"/>
+      <c r="I135" s="7" t="n"/>
+      <c r="J135" s="7" t="n"/>
+    </row>
+    <row r="136" ht="19" customHeight="1">
+      <c r="A136" s="8" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" s="9" t="n"/>
+      <c r="C136" s="9" t="n"/>
+      <c r="D136" s="9" t="n"/>
+      <c r="E136" s="9" t="n"/>
+      <c r="F136" s="9" t="n"/>
+      <c r="G136" s="9" t="n"/>
+      <c r="H136" s="9" t="n"/>
+      <c r="I136" s="9" t="n"/>
+      <c r="J136" s="9" t="n"/>
+    </row>
+    <row r="137" ht="19" customHeight="1">
+      <c r="A137" s="6" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" s="7" t="n"/>
+      <c r="C137" s="7" t="n"/>
+      <c r="D137" s="7" t="n"/>
+      <c r="E137" s="7" t="n"/>
+      <c r="F137" s="7" t="n"/>
+      <c r="G137" s="7" t="n"/>
+      <c r="H137" s="7" t="n"/>
+      <c r="I137" s="7" t="n"/>
+      <c r="J137" s="7" t="n"/>
+    </row>
+    <row r="138" ht="19" customHeight="1">
+      <c r="A138" s="8" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" s="9" t="n"/>
+      <c r="C138" s="9" t="n"/>
+      <c r="D138" s="9" t="n"/>
+      <c r="E138" s="9" t="n"/>
+      <c r="F138" s="9" t="n"/>
+      <c r="G138" s="9" t="n"/>
+      <c r="H138" s="9" t="n"/>
+      <c r="I138" s="9" t="n"/>
+      <c r="J138" s="9" t="n"/>
+    </row>
+    <row r="139" ht="19" customHeight="1">
+      <c r="A139" s="6" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" s="7" t="n"/>
+      <c r="C139" s="7" t="n"/>
+      <c r="D139" s="7" t="n"/>
+      <c r="E139" s="7" t="n"/>
+      <c r="F139" s="7" t="n"/>
+      <c r="G139" s="7" t="n"/>
+      <c r="H139" s="7" t="n"/>
+      <c r="I139" s="7" t="n"/>
+      <c r="J139" s="7" t="n"/>
+    </row>
+    <row r="140" ht="19" customHeight="1">
+      <c r="A140" s="8" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" s="9" t="n"/>
+      <c r="C140" s="9" t="n"/>
+      <c r="D140" s="9" t="n"/>
+      <c r="E140" s="9" t="n"/>
+      <c r="F140" s="9" t="n"/>
+      <c r="G140" s="9" t="n"/>
+      <c r="H140" s="9" t="n"/>
+      <c r="I140" s="9" t="n"/>
+      <c r="J140" s="9" t="n"/>
+    </row>
+    <row r="141" ht="19" customHeight="1">
+      <c r="A141" s="6" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" s="7" t="n"/>
+      <c r="C141" s="7" t="n"/>
+      <c r="D141" s="7" t="n"/>
+      <c r="E141" s="7" t="n"/>
+      <c r="F141" s="7" t="n"/>
+      <c r="G141" s="7" t="n"/>
+      <c r="H141" s="7" t="n"/>
+      <c r="I141" s="7" t="n"/>
+      <c r="J141" s="7" t="n"/>
+    </row>
+    <row r="142" ht="19" customHeight="1">
+      <c r="A142" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" s="9" t="n"/>
+      <c r="C142" s="9" t="n"/>
+      <c r="D142" s="9" t="n"/>
+      <c r="E142" s="9" t="n"/>
+      <c r="F142" s="9" t="n"/>
+      <c r="G142" s="9" t="n"/>
+      <c r="H142" s="9" t="n"/>
+      <c r="I142" s="9" t="n"/>
+      <c r="J142" s="9" t="n"/>
+    </row>
+    <row r="143" ht="19" customHeight="1">
+      <c r="A143" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" s="7" t="n"/>
+      <c r="C143" s="7" t="n"/>
+      <c r="D143" s="7" t="n"/>
+      <c r="E143" s="7" t="n"/>
+      <c r="F143" s="7" t="n"/>
+      <c r="G143" s="7" t="n"/>
+      <c r="H143" s="7" t="n"/>
+      <c r="I143" s="7" t="n"/>
+      <c r="J143" s="7" t="n"/>
+    </row>
+    <row r="144" ht="19" customHeight="1">
+      <c r="A144" s="8" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="9" t="n"/>
+      <c r="C144" s="9" t="n"/>
+      <c r="D144" s="9" t="n"/>
+      <c r="E144" s="9" t="n"/>
+      <c r="F144" s="9" t="n"/>
+      <c r="G144" s="9" t="n"/>
+      <c r="H144" s="9" t="n"/>
+      <c r="I144" s="9" t="n"/>
+      <c r="J144" s="9" t="n"/>
+    </row>
+    <row r="145" ht="19" customHeight="1">
+      <c r="A145" s="6" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="7" t="n"/>
+      <c r="C145" s="7" t="n"/>
+      <c r="D145" s="7" t="n"/>
+      <c r="E145" s="7" t="n"/>
+      <c r="F145" s="7" t="n"/>
+      <c r="G145" s="7" t="n"/>
+      <c r="H145" s="7" t="n"/>
+      <c r="I145" s="7" t="n"/>
+      <c r="J145" s="7" t="n"/>
+    </row>
+    <row r="146" ht="19" customHeight="1">
+      <c r="A146" s="8" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="9" t="n"/>
+      <c r="C146" s="9" t="n"/>
+      <c r="D146" s="9" t="n"/>
+      <c r="E146" s="9" t="n"/>
+      <c r="F146" s="9" t="n"/>
+      <c r="G146" s="9" t="n"/>
+      <c r="H146" s="9" t="n"/>
+      <c r="I146" s="9" t="n"/>
+      <c r="J146" s="9" t="n"/>
+    </row>
+    <row r="147" ht="19" customHeight="1">
+      <c r="A147" s="6" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="7" t="n"/>
+      <c r="C147" s="7" t="n"/>
+      <c r="D147" s="7" t="n"/>
+      <c r="E147" s="7" t="n"/>
+      <c r="F147" s="7" t="n"/>
+      <c r="G147" s="7" t="n"/>
+      <c r="H147" s="7" t="n"/>
+      <c r="I147" s="7" t="n"/>
+      <c r="J147" s="7" t="n"/>
+    </row>
+    <row r="148" ht="19" customHeight="1">
+      <c r="A148" s="8" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" s="9" t="n"/>
+      <c r="C148" s="9" t="n"/>
+      <c r="D148" s="9" t="n"/>
+      <c r="E148" s="9" t="n"/>
+      <c r="F148" s="9" t="n"/>
+      <c r="G148" s="9" t="n"/>
+      <c r="H148" s="9" t="n"/>
+      <c r="I148" s="9" t="n"/>
+      <c r="J148" s="9" t="n"/>
+    </row>
+    <row r="149" ht="19" customHeight="1">
+      <c r="A149" s="6" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" s="7" t="n"/>
+      <c r="C149" s="7" t="n"/>
+      <c r="D149" s="7" t="n"/>
+      <c r="E149" s="7" t="n"/>
+      <c r="F149" s="7" t="n"/>
+      <c r="G149" s="7" t="n"/>
+      <c r="H149" s="7" t="n"/>
+      <c r="I149" s="7" t="n"/>
+      <c r="J149" s="7" t="n"/>
+    </row>
+    <row r="150" ht="19" customHeight="1">
+      <c r="A150" s="8" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" s="9" t="n"/>
+      <c r="C150" s="9" t="n"/>
+      <c r="D150" s="9" t="n"/>
+      <c r="E150" s="9" t="n"/>
+      <c r="F150" s="9" t="n"/>
+      <c r="G150" s="9" t="n"/>
+      <c r="H150" s="9" t="n"/>
+      <c r="I150" s="9" t="n"/>
+      <c r="J150" s="9" t="n"/>
+    </row>
+    <row r="151" ht="19" customHeight="1">
+      <c r="A151" s="6" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" s="7" t="n"/>
+      <c r="C151" s="7" t="n"/>
+      <c r="D151" s="7" t="n"/>
+      <c r="E151" s="7" t="n"/>
+      <c r="F151" s="7" t="n"/>
+      <c r="G151" s="7" t="n"/>
+      <c r="H151" s="7" t="n"/>
+      <c r="I151" s="7" t="n"/>
+      <c r="J151" s="7" t="n"/>
+    </row>
+    <row r="152" ht="19" customHeight="1">
+      <c r="A152" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="9" t="n"/>
+      <c r="C152" s="9" t="n"/>
+      <c r="D152" s="9" t="n"/>
+      <c r="E152" s="9" t="n"/>
+      <c r="F152" s="9" t="n"/>
+      <c r="G152" s="9" t="n"/>
+      <c r="H152" s="9" t="n"/>
+      <c r="I152" s="9" t="n"/>
+      <c r="J152" s="9" t="n"/>
+    </row>
+    <row r="153" ht="19" customHeight="1">
+      <c r="A153" s="6" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" s="7" t="n"/>
+      <c r="C153" s="7" t="n"/>
+      <c r="D153" s="7" t="n"/>
+      <c r="E153" s="7" t="n"/>
+      <c r="F153" s="7" t="n"/>
+      <c r="G153" s="7" t="n"/>
+      <c r="H153" s="7" t="n"/>
+      <c r="I153" s="7" t="n"/>
+      <c r="J153" s="7" t="n"/>
+    </row>
+    <row r="154" ht="19" customHeight="1">
+      <c r="A154" s="8" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" s="9" t="n"/>
+      <c r="C154" s="9" t="n"/>
+      <c r="D154" s="9" t="n"/>
+      <c r="E154" s="9" t="n"/>
+      <c r="F154" s="9" t="n"/>
+      <c r="G154" s="9" t="n"/>
+      <c r="H154" s="9" t="n"/>
+      <c r="I154" s="9" t="n"/>
+      <c r="J154" s="9" t="n"/>
+    </row>
+    <row r="155" ht="19" customHeight="1">
+      <c r="A155" s="6" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" s="7" t="n"/>
+      <c r="C155" s="7" t="n"/>
+      <c r="D155" s="7" t="n"/>
+      <c r="E155" s="7" t="n"/>
+      <c r="F155" s="7" t="n"/>
+      <c r="G155" s="7" t="n"/>
+      <c r="H155" s="7" t="n"/>
+      <c r="I155" s="7" t="n"/>
+      <c r="J155" s="7" t="n"/>
+    </row>
+    <row r="156" ht="19" customHeight="1">
+      <c r="A156" s="8" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" s="9" t="n"/>
+      <c r="C156" s="9" t="n"/>
+      <c r="D156" s="9" t="n"/>
+      <c r="E156" s="9" t="n"/>
+      <c r="F156" s="9" t="n"/>
+      <c r="G156" s="9" t="n"/>
+      <c r="H156" s="9" t="n"/>
+      <c r="I156" s="9" t="n"/>
+      <c r="J156" s="9" t="n"/>
+    </row>
+    <row r="157" ht="19" customHeight="1">
+      <c r="A157" s="6" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" s="7" t="n"/>
+      <c r="C157" s="7" t="n"/>
+      <c r="D157" s="7" t="n"/>
+      <c r="E157" s="7" t="n"/>
+      <c r="F157" s="7" t="n"/>
+      <c r="G157" s="7" t="n"/>
+      <c r="H157" s="7" t="n"/>
+      <c r="I157" s="7" t="n"/>
+      <c r="J157" s="7" t="n"/>
+    </row>
+    <row r="158" ht="19" customHeight="1">
+      <c r="A158" s="8" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" s="9" t="n"/>
+      <c r="C158" s="9" t="n"/>
+      <c r="D158" s="9" t="n"/>
+      <c r="E158" s="9" t="n"/>
+      <c r="F158" s="9" t="n"/>
+      <c r="G158" s="9" t="n"/>
+      <c r="H158" s="9" t="n"/>
+      <c r="I158" s="9" t="n"/>
+      <c r="J158" s="9" t="n"/>
+    </row>
+    <row r="159" ht="19" customHeight="1">
+      <c r="A159" s="6" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" s="7" t="n"/>
+      <c r="C159" s="7" t="n"/>
+      <c r="D159" s="7" t="n"/>
+      <c r="E159" s="7" t="n"/>
+      <c r="F159" s="7" t="n"/>
+      <c r="G159" s="7" t="n"/>
+      <c r="H159" s="7" t="n"/>
+      <c r="I159" s="7" t="n"/>
+      <c r="J159" s="7" t="n"/>
+    </row>
+    <row r="160" ht="19" customHeight="1">
+      <c r="A160" s="8" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" s="9" t="n"/>
+      <c r="C160" s="9" t="n"/>
+      <c r="D160" s="9" t="n"/>
+      <c r="E160" s="9" t="n"/>
+      <c r="F160" s="9" t="n"/>
+      <c r="G160" s="9" t="n"/>
+      <c r="H160" s="9" t="n"/>
+      <c r="I160" s="9" t="n"/>
+      <c r="J160" s="9" t="n"/>
+    </row>
+    <row r="161" ht="19" customHeight="1">
+      <c r="A161" s="6" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" s="7" t="n"/>
+      <c r="C161" s="7" t="n"/>
+      <c r="D161" s="7" t="n"/>
+      <c r="E161" s="7" t="n"/>
+      <c r="F161" s="7" t="n"/>
+      <c r="G161" s="7" t="n"/>
+      <c r="H161" s="7" t="n"/>
+      <c r="I161" s="7" t="n"/>
+      <c r="J161" s="7" t="n"/>
+    </row>
+    <row r="162" ht="19" customHeight="1">
+      <c r="A162" s="8" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" s="9" t="n"/>
+      <c r="C162" s="9" t="n"/>
+      <c r="D162" s="9" t="n"/>
+      <c r="E162" s="9" t="n"/>
+      <c r="F162" s="9" t="n"/>
+      <c r="G162" s="9" t="n"/>
+      <c r="H162" s="9" t="n"/>
+      <c r="I162" s="9" t="n"/>
+      <c r="J162" s="9" t="n"/>
+    </row>
+    <row r="163" ht="19" customHeight="1">
+      <c r="A163" s="6" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" s="7" t="n"/>
+      <c r="C163" s="7" t="n"/>
+      <c r="D163" s="7" t="n"/>
+      <c r="E163" s="7" t="n"/>
+      <c r="F163" s="7" t="n"/>
+      <c r="G163" s="7" t="n"/>
+      <c r="H163" s="7" t="n"/>
+      <c r="I163" s="7" t="n"/>
+      <c r="J163" s="7" t="n"/>
+    </row>
+    <row r="164" ht="19" customHeight="1">
+      <c r="A164" s="8" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" s="9" t="n"/>
+      <c r="C164" s="9" t="n"/>
+      <c r="D164" s="9" t="n"/>
+      <c r="E164" s="9" t="n"/>
+      <c r="F164" s="9" t="n"/>
+      <c r="G164" s="9" t="n"/>
+      <c r="H164" s="9" t="n"/>
+      <c r="I164" s="9" t="n"/>
+      <c r="J164" s="9" t="n"/>
+    </row>
+    <row r="165" ht="19" customHeight="1">
+      <c r="A165" s="6" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" s="7" t="n"/>
+      <c r="C165" s="7" t="n"/>
+      <c r="D165" s="7" t="n"/>
+      <c r="E165" s="7" t="n"/>
+      <c r="F165" s="7" t="n"/>
+      <c r="G165" s="7" t="n"/>
+      <c r="H165" s="7" t="n"/>
+      <c r="I165" s="7" t="n"/>
+      <c r="J165" s="7" t="n"/>
+    </row>
+    <row r="166" ht="19" customHeight="1">
+      <c r="A166" s="8" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" s="9" t="n"/>
+      <c r="C166" s="9" t="n"/>
+      <c r="D166" s="9" t="n"/>
+      <c r="E166" s="9" t="n"/>
+      <c r="F166" s="9" t="n"/>
+      <c r="G166" s="9" t="n"/>
+      <c r="H166" s="9" t="n"/>
+      <c r="I166" s="9" t="n"/>
+      <c r="J166" s="9" t="n"/>
+    </row>
+    <row r="167" ht="19" customHeight="1">
+      <c r="A167" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" s="7" t="n"/>
+      <c r="C167" s="7" t="n"/>
+      <c r="D167" s="7" t="n"/>
+      <c r="E167" s="7" t="n"/>
+      <c r="F167" s="7" t="n"/>
+      <c r="G167" s="7" t="n"/>
+      <c r="H167" s="7" t="n"/>
+      <c r="I167" s="7" t="n"/>
+      <c r="J167" s="7" t="n"/>
+    </row>
+    <row r="168" ht="19" customHeight="1">
+      <c r="A168" s="8" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" s="9" t="n"/>
+      <c r="C168" s="9" t="n"/>
+      <c r="D168" s="9" t="n"/>
+      <c r="E168" s="9" t="n"/>
+      <c r="F168" s="9" t="n"/>
+      <c r="G168" s="9" t="n"/>
+      <c r="H168" s="9" t="n"/>
+      <c r="I168" s="9" t="n"/>
+      <c r="J168" s="9" t="n"/>
+    </row>
+    <row r="169" ht="19" customHeight="1">
+      <c r="A169" s="6" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" s="7" t="n"/>
+      <c r="C169" s="7" t="n"/>
+      <c r="D169" s="7" t="n"/>
+      <c r="E169" s="7" t="n"/>
+      <c r="F169" s="7" t="n"/>
+      <c r="G169" s="7" t="n"/>
+      <c r="H169" s="7" t="n"/>
+      <c r="I169" s="7" t="n"/>
+      <c r="J169" s="7" t="n"/>
+    </row>
+    <row r="170" ht="19" customHeight="1">
+      <c r="A170" s="8" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" s="9" t="n"/>
+      <c r="C170" s="9" t="n"/>
+      <c r="D170" s="9" t="n"/>
+      <c r="E170" s="9" t="n"/>
+      <c r="F170" s="9" t="n"/>
+      <c r="G170" s="9" t="n"/>
+      <c r="H170" s="9" t="n"/>
+      <c r="I170" s="9" t="n"/>
+      <c r="J170" s="9" t="n"/>
+    </row>
+    <row r="171" ht="19" customHeight="1">
+      <c r="A171" s="6" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" s="7" t="n"/>
+      <c r="C171" s="7" t="n"/>
+      <c r="D171" s="7" t="n"/>
+      <c r="E171" s="7" t="n"/>
+      <c r="F171" s="7" t="n"/>
+      <c r="G171" s="7" t="n"/>
+      <c r="H171" s="7" t="n"/>
+      <c r="I171" s="7" t="n"/>
+      <c r="J171" s="7" t="n"/>
+    </row>
+    <row r="172" ht="19" customHeight="1">
+      <c r="A172" s="8" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" s="9" t="n"/>
+      <c r="C172" s="9" t="n"/>
+      <c r="D172" s="9" t="n"/>
+      <c r="E172" s="9" t="n"/>
+      <c r="F172" s="9" t="n"/>
+      <c r="G172" s="9" t="n"/>
+      <c r="H172" s="9" t="n"/>
+      <c r="I172" s="9" t="n"/>
+      <c r="J172" s="9" t="n"/>
+    </row>
+    <row r="173" ht="19" customHeight="1">
+      <c r="A173" s="6" t="n">
+        <v>171</v>
+      </c>
+      <c r="B173" s="7" t="n"/>
+      <c r="C173" s="7" t="n"/>
+      <c r="D173" s="7" t="n"/>
+      <c r="E173" s="7" t="n"/>
+      <c r="F173" s="7" t="n"/>
+      <c r="G173" s="7" t="n"/>
+      <c r="H173" s="7" t="n"/>
+      <c r="I173" s="7" t="n"/>
+      <c r="J173" s="7" t="n"/>
+    </row>
+    <row r="174" ht="19" customHeight="1">
+      <c r="A174" s="8" t="n">
+        <v>172</v>
+      </c>
+      <c r="B174" s="9" t="n"/>
+      <c r="C174" s="9" t="n"/>
+      <c r="D174" s="9" t="n"/>
+      <c r="E174" s="9" t="n"/>
+      <c r="F174" s="9" t="n"/>
+      <c r="G174" s="9" t="n"/>
+      <c r="H174" s="9" t="n"/>
+      <c r="I174" s="9" t="n"/>
+      <c r="J174" s="9" t="n"/>
+    </row>
+    <row r="175" ht="19" customHeight="1">
+      <c r="A175" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="B175" s="7" t="n"/>
+      <c r="C175" s="7" t="n"/>
+      <c r="D175" s="7" t="n"/>
+      <c r="E175" s="7" t="n"/>
+      <c r="F175" s="7" t="n"/>
+      <c r="G175" s="7" t="n"/>
+      <c r="H175" s="7" t="n"/>
+      <c r="I175" s="7" t="n"/>
+      <c r="J175" s="7" t="n"/>
+    </row>
+    <row r="176" ht="19" customHeight="1">
+      <c r="A176" s="8" t="n">
+        <v>174</v>
+      </c>
+      <c r="B176" s="9" t="n"/>
+      <c r="C176" s="9" t="n"/>
+      <c r="D176" s="9" t="n"/>
+      <c r="E176" s="9" t="n"/>
+      <c r="F176" s="9" t="n"/>
+      <c r="G176" s="9" t="n"/>
+      <c r="H176" s="9" t="n"/>
+      <c r="I176" s="9" t="n"/>
+      <c r="J176" s="9" t="n"/>
+    </row>
+    <row r="177" ht="19" customHeight="1">
+      <c r="A177" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" s="7" t="n"/>
+      <c r="C177" s="7" t="n"/>
+      <c r="D177" s="7" t="n"/>
+      <c r="E177" s="7" t="n"/>
+      <c r="F177" s="7" t="n"/>
+      <c r="G177" s="7" t="n"/>
+      <c r="H177" s="7" t="n"/>
+      <c r="I177" s="7" t="n"/>
+      <c r="J177" s="7" t="n"/>
+    </row>
+    <row r="178" ht="19" customHeight="1">
+      <c r="A178" s="8" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" s="9" t="n"/>
+      <c r="C178" s="9" t="n"/>
+      <c r="D178" s="9" t="n"/>
+      <c r="E178" s="9" t="n"/>
+      <c r="F178" s="9" t="n"/>
+      <c r="G178" s="9" t="n"/>
+      <c r="H178" s="9" t="n"/>
+      <c r="I178" s="9" t="n"/>
+      <c r="J178" s="9" t="n"/>
+    </row>
+    <row r="179" ht="19" customHeight="1">
+      <c r="A179" s="6" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" s="7" t="n"/>
+      <c r="C179" s="7" t="n"/>
+      <c r="D179" s="7" t="n"/>
+      <c r="E179" s="7" t="n"/>
+      <c r="F179" s="7" t="n"/>
+      <c r="G179" s="7" t="n"/>
+      <c r="H179" s="7" t="n"/>
+      <c r="I179" s="7" t="n"/>
+      <c r="J179" s="7" t="n"/>
+    </row>
+    <row r="180" ht="19" customHeight="1">
+      <c r="A180" s="8" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" s="9" t="n"/>
+      <c r="C180" s="9" t="n"/>
+      <c r="D180" s="9" t="n"/>
+      <c r="E180" s="9" t="n"/>
+      <c r="F180" s="9" t="n"/>
+      <c r="G180" s="9" t="n"/>
+      <c r="H180" s="9" t="n"/>
+      <c r="I180" s="9" t="n"/>
+      <c r="J180" s="9" t="n"/>
+    </row>
+    <row r="181" ht="19" customHeight="1">
+      <c r="A181" s="6" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" s="7" t="n"/>
+      <c r="C181" s="7" t="n"/>
+      <c r="D181" s="7" t="n"/>
+      <c r="E181" s="7" t="n"/>
+      <c r="F181" s="7" t="n"/>
+      <c r="G181" s="7" t="n"/>
+      <c r="H181" s="7" t="n"/>
+      <c r="I181" s="7" t="n"/>
+      <c r="J181" s="7" t="n"/>
+    </row>
+    <row r="182" ht="19" customHeight="1">
+      <c r="A182" s="8" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" s="9" t="n"/>
+      <c r="C182" s="9" t="n"/>
+      <c r="D182" s="9" t="n"/>
+      <c r="E182" s="9" t="n"/>
+      <c r="F182" s="9" t="n"/>
+      <c r="G182" s="9" t="n"/>
+      <c r="H182" s="9" t="n"/>
+      <c r="I182" s="9" t="n"/>
+      <c r="J182" s="9" t="n"/>
+    </row>
+    <row r="183" ht="19" customHeight="1">
+      <c r="A183" s="6" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" s="7" t="n"/>
+      <c r="C183" s="7" t="n"/>
+      <c r="D183" s="7" t="n"/>
+      <c r="E183" s="7" t="n"/>
+      <c r="F183" s="7" t="n"/>
+      <c r="G183" s="7" t="n"/>
+      <c r="H183" s="7" t="n"/>
+      <c r="I183" s="7" t="n"/>
+      <c r="J183" s="7" t="n"/>
+    </row>
+    <row r="184" ht="19" customHeight="1">
+      <c r="A184" s="8" t="n">
+        <v>182</v>
+      </c>
+      <c r="B184" s="9" t="n"/>
+      <c r="C184" s="9" t="n"/>
+      <c r="D184" s="9" t="n"/>
+      <c r="E184" s="9" t="n"/>
+      <c r="F184" s="9" t="n"/>
+      <c r="G184" s="9" t="n"/>
+      <c r="H184" s="9" t="n"/>
+      <c r="I184" s="9" t="n"/>
+      <c r="J184" s="9" t="n"/>
+    </row>
+    <row r="185" ht="19" customHeight="1">
+      <c r="A185" s="6" t="n">
+        <v>183</v>
+      </c>
+      <c r="B185" s="7" t="n"/>
+      <c r="C185" s="7" t="n"/>
+      <c r="D185" s="7" t="n"/>
+      <c r="E185" s="7" t="n"/>
+      <c r="F185" s="7" t="n"/>
+      <c r="G185" s="7" t="n"/>
+      <c r="H185" s="7" t="n"/>
+      <c r="I185" s="7" t="n"/>
+      <c r="J185" s="7" t="n"/>
+    </row>
+    <row r="186" ht="19" customHeight="1">
+      <c r="A186" s="8" t="n">
+        <v>184</v>
+      </c>
+      <c r="B186" s="9" t="n"/>
+      <c r="C186" s="9" t="n"/>
+      <c r="D186" s="9" t="n"/>
+      <c r="E186" s="9" t="n"/>
+      <c r="F186" s="9" t="n"/>
+      <c r="G186" s="9" t="n"/>
+      <c r="H186" s="9" t="n"/>
+      <c r="I186" s="9" t="n"/>
+      <c r="J186" s="9" t="n"/>
+    </row>
+    <row r="187" ht="19" customHeight="1">
+      <c r="A187" s="6" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" s="7" t="n"/>
+      <c r="C187" s="7" t="n"/>
+      <c r="D187" s="7" t="n"/>
+      <c r="E187" s="7" t="n"/>
+      <c r="F187" s="7" t="n"/>
+      <c r="G187" s="7" t="n"/>
+      <c r="H187" s="7" t="n"/>
+      <c r="I187" s="7" t="n"/>
+      <c r="J187" s="7" t="n"/>
+    </row>
+    <row r="188" ht="19" customHeight="1">
+      <c r="A188" s="8" t="n">
+        <v>186</v>
+      </c>
+      <c r="B188" s="9" t="n"/>
+      <c r="C188" s="9" t="n"/>
+      <c r="D188" s="9" t="n"/>
+      <c r="E188" s="9" t="n"/>
+      <c r="F188" s="9" t="n"/>
+      <c r="G188" s="9" t="n"/>
+      <c r="H188" s="9" t="n"/>
+      <c r="I188" s="9" t="n"/>
+      <c r="J188" s="9" t="n"/>
+    </row>
+    <row r="189" ht="19" customHeight="1">
+      <c r="A189" s="6" t="n">
+        <v>187</v>
+      </c>
+      <c r="B189" s="7" t="n"/>
+      <c r="C189" s="7" t="n"/>
+      <c r="D189" s="7" t="n"/>
+      <c r="E189" s="7" t="n"/>
+      <c r="F189" s="7" t="n"/>
+      <c r="G189" s="7" t="n"/>
+      <c r="H189" s="7" t="n"/>
+      <c r="I189" s="7" t="n"/>
+      <c r="J189" s="7" t="n"/>
+    </row>
+    <row r="190" ht="19" customHeight="1">
+      <c r="A190" s="8" t="n">
+        <v>188</v>
+      </c>
+      <c r="B190" s="9" t="n"/>
+      <c r="C190" s="9" t="n"/>
+      <c r="D190" s="9" t="n"/>
+      <c r="E190" s="9" t="n"/>
+      <c r="F190" s="9" t="n"/>
+      <c r="G190" s="9" t="n"/>
+      <c r="H190" s="9" t="n"/>
+      <c r="I190" s="9" t="n"/>
+      <c r="J190" s="9" t="n"/>
+    </row>
+    <row r="191" ht="19" customHeight="1">
+      <c r="A191" s="6" t="n">
+        <v>189</v>
+      </c>
+      <c r="B191" s="7" t="n"/>
+      <c r="C191" s="7" t="n"/>
+      <c r="D191" s="7" t="n"/>
+      <c r="E191" s="7" t="n"/>
+      <c r="F191" s="7" t="n"/>
+      <c r="G191" s="7" t="n"/>
+      <c r="H191" s="7" t="n"/>
+      <c r="I191" s="7" t="n"/>
+      <c r="J191" s="7" t="n"/>
+    </row>
+    <row r="192" ht="19" customHeight="1">
+      <c r="A192" s="8" t="n">
+        <v>190</v>
+      </c>
+      <c r="B192" s="9" t="n"/>
+      <c r="C192" s="9" t="n"/>
+      <c r="D192" s="9" t="n"/>
+      <c r="E192" s="9" t="n"/>
+      <c r="F192" s="9" t="n"/>
+      <c r="G192" s="9" t="n"/>
+      <c r="H192" s="9" t="n"/>
+      <c r="I192" s="9" t="n"/>
+      <c r="J192" s="9" t="n"/>
+    </row>
+    <row r="193" ht="19" customHeight="1">
+      <c r="A193" s="6" t="n">
+        <v>191</v>
+      </c>
+      <c r="B193" s="7" t="n"/>
+      <c r="C193" s="7" t="n"/>
+      <c r="D193" s="7" t="n"/>
+      <c r="E193" s="7" t="n"/>
+      <c r="F193" s="7" t="n"/>
+      <c r="G193" s="7" t="n"/>
+      <c r="H193" s="7" t="n"/>
+      <c r="I193" s="7" t="n"/>
+      <c r="J193" s="7" t="n"/>
+    </row>
+    <row r="194" ht="19" customHeight="1">
+      <c r="A194" s="8" t="n">
+        <v>192</v>
+      </c>
+      <c r="B194" s="9" t="n"/>
+      <c r="C194" s="9" t="n"/>
+      <c r="D194" s="9" t="n"/>
+      <c r="E194" s="9" t="n"/>
+      <c r="F194" s="9" t="n"/>
+      <c r="G194" s="9" t="n"/>
+      <c r="H194" s="9" t="n"/>
+      <c r="I194" s="9" t="n"/>
+      <c r="J194" s="9" t="n"/>
+    </row>
+    <row r="195" ht="19" customHeight="1">
+      <c r="A195" s="6" t="n">
+        <v>193</v>
+      </c>
+      <c r="B195" s="7" t="n"/>
+      <c r="C195" s="7" t="n"/>
+      <c r="D195" s="7" t="n"/>
+      <c r="E195" s="7" t="n"/>
+      <c r="F195" s="7" t="n"/>
+      <c r="G195" s="7" t="n"/>
+      <c r="H195" s="7" t="n"/>
+      <c r="I195" s="7" t="n"/>
+      <c r="J195" s="7" t="n"/>
+    </row>
+    <row r="196" ht="19" customHeight="1">
+      <c r="A196" s="8" t="n">
+        <v>194</v>
+      </c>
+      <c r="B196" s="9" t="n"/>
+      <c r="C196" s="9" t="n"/>
+      <c r="D196" s="9" t="n"/>
+      <c r="E196" s="9" t="n"/>
+      <c r="F196" s="9" t="n"/>
+      <c r="G196" s="9" t="n"/>
+      <c r="H196" s="9" t="n"/>
+      <c r="I196" s="9" t="n"/>
+      <c r="J196" s="9" t="n"/>
+    </row>
+    <row r="197" ht="19" customHeight="1">
+      <c r="A197" s="6" t="n">
+        <v>195</v>
+      </c>
+      <c r="B197" s="7" t="n"/>
+      <c r="C197" s="7" t="n"/>
+      <c r="D197" s="7" t="n"/>
+      <c r="E197" s="7" t="n"/>
+      <c r="F197" s="7" t="n"/>
+      <c r="G197" s="7" t="n"/>
+      <c r="H197" s="7" t="n"/>
+      <c r="I197" s="7" t="n"/>
+      <c r="J197" s="7" t="n"/>
+    </row>
+    <row r="198" ht="19" customHeight="1">
+      <c r="A198" s="8" t="n">
+        <v>196</v>
+      </c>
+      <c r="B198" s="9" t="n"/>
+      <c r="C198" s="9" t="n"/>
+      <c r="D198" s="9" t="n"/>
+      <c r="E198" s="9" t="n"/>
+      <c r="F198" s="9" t="n"/>
+      <c r="G198" s="9" t="n"/>
+      <c r="H198" s="9" t="n"/>
+      <c r="I198" s="9" t="n"/>
+      <c r="J198" s="9" t="n"/>
+    </row>
+    <row r="199" ht="19" customHeight="1">
+      <c r="A199" s="6" t="n">
+        <v>197</v>
+      </c>
+      <c r="B199" s="7" t="n"/>
+      <c r="C199" s="7" t="n"/>
+      <c r="D199" s="7" t="n"/>
+      <c r="E199" s="7" t="n"/>
+      <c r="F199" s="7" t="n"/>
+      <c r="G199" s="7" t="n"/>
+      <c r="H199" s="7" t="n"/>
+      <c r="I199" s="7" t="n"/>
+      <c r="J199" s="7" t="n"/>
+    </row>
+    <row r="200" ht="19" customHeight="1">
+      <c r="A200" s="8" t="n">
+        <v>198</v>
+      </c>
+      <c r="B200" s="9" t="n"/>
+      <c r="C200" s="9" t="n"/>
+      <c r="D200" s="9" t="n"/>
+      <c r="E200" s="9" t="n"/>
+      <c r="F200" s="9" t="n"/>
+      <c r="G200" s="9" t="n"/>
+      <c r="H200" s="9" t="n"/>
+      <c r="I200" s="9" t="n"/>
+      <c r="J200" s="9" t="n"/>
+    </row>
+    <row r="201" ht="19" customHeight="1">
+      <c r="A201" s="6" t="n">
+        <v>199</v>
+      </c>
+      <c r="B201" s="7" t="n"/>
+      <c r="C201" s="7" t="n"/>
+      <c r="D201" s="7" t="n"/>
+      <c r="E201" s="7" t="n"/>
+      <c r="F201" s="7" t="n"/>
+      <c r="G201" s="7" t="n"/>
+      <c r="H201" s="7" t="n"/>
+      <c r="I201" s="7" t="n"/>
+      <c r="J201" s="7" t="n"/>
+    </row>
+    <row r="202" ht="19" customHeight="1">
+      <c r="A202" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="B202" s="9" t="n"/>
+      <c r="C202" s="9" t="n"/>
+      <c r="D202" s="9" t="n"/>
+      <c r="E202" s="9" t="n"/>
+      <c r="F202" s="9" t="n"/>
+      <c r="G202" s="9" t="n"/>
+      <c r="H202" s="9" t="n"/>
+      <c r="I202" s="9" t="n"/>
+      <c r="J202" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="I3:I92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H3:H202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="J3:J92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I3:I202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3458,25 +4902,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:V62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="44" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>※ 서류 합격자 발표 10. 12.(월) · 합격 팀에 이메일 개별 통보</t>
+          <t>※ 배점 : 문제 정의 10 · AI 솔루션 적합성 20 · 시장 규모 15 · 비즈니스 모델 타당성 20 · 구현 계획 20 · 사업 의지 15 = 100점  ｜  서류 합격자 발표 10. 12.(월) 이메일 개별 통보</t>
         </is>
       </c>
     </row>
@@ -3498,38 +4954,110 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>심사위원 1
-점수</t>
+          <t>심사1
+문제 정의 능력</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>심사위원 2
-점수</t>
+          <t>심사1
+AI 솔루션 적합성</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
+          <t>심사1
+시장 규모</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>심사1
+비즈니스 모델 타당성</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>심사1
+구현 계획</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>심사1
+사업 의지</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>심사2
+문제 정의 능력</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>심사2
+AI 솔루션 적합성</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>심사2
+시장 규모</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>심사2
+비즈니스 모델 타당성</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>심사2
+구현 계획</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>심사2
+사업 의지</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>심사 1
+소계</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>심사 2
+소계</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
           <t>평균</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="S2" s="5" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="T2" s="5" t="inlineStr">
         <is>
           <t>합격
 여부</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="U2" s="5" t="inlineStr">
         <is>
           <t>통보일</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="V2" s="5" t="inlineStr">
         <is>
           <t>심사 의견</t>
         </is>
@@ -3543,14 +5071,32 @@
       <c r="C3" s="7" t="n"/>
       <c r="D3" s="7" t="n"/>
       <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7">
-        <f>IF(COUNT(D3:E3)=0,"",ROUND(AVERAGE(D3:E3),1))</f>
-        <v/>
-      </c>
+      <c r="F3" s="7" t="n"/>
       <c r="G3" s="7" t="n"/>
       <c r="H3" s="7" t="n"/>
       <c r="I3" s="7" t="n"/>
       <c r="J3" s="7" t="n"/>
+      <c r="K3" s="7" t="n"/>
+      <c r="L3" s="7" t="n"/>
+      <c r="M3" s="7" t="n"/>
+      <c r="N3" s="7" t="n"/>
+      <c r="O3" s="7" t="n"/>
+      <c r="P3" s="7">
+        <f>IF(COUNT(D3:I3)=0,"",SUM(D3:I3))</f>
+        <v/>
+      </c>
+      <c r="Q3" s="7">
+        <f>IF(COUNT(J3:O3)=0,"",SUM(J3:O3))</f>
+        <v/>
+      </c>
+      <c r="R3" s="7">
+        <f>IF(COUNT(P3:Q3)=0,"",ROUND(AVERAGE(P3:Q3),1))</f>
+        <v/>
+      </c>
+      <c r="S3" s="7" t="n"/>
+      <c r="T3" s="7" t="n"/>
+      <c r="U3" s="7" t="n"/>
+      <c r="V3" s="7" t="n"/>
     </row>
     <row r="4" ht="19" customHeight="1">
       <c r="A4" s="8" t="n">
@@ -3560,14 +5106,32 @@
       <c r="C4" s="9" t="n"/>
       <c r="D4" s="9" t="n"/>
       <c r="E4" s="9" t="n"/>
-      <c r="F4" s="9">
-        <f>IF(COUNT(D4:E4)=0,"",ROUND(AVERAGE(D4:E4),1))</f>
-        <v/>
-      </c>
+      <c r="F4" s="9" t="n"/>
       <c r="G4" s="9" t="n"/>
       <c r="H4" s="9" t="n"/>
       <c r="I4" s="9" t="n"/>
       <c r="J4" s="9" t="n"/>
+      <c r="K4" s="9" t="n"/>
+      <c r="L4" s="9" t="n"/>
+      <c r="M4" s="9" t="n"/>
+      <c r="N4" s="9" t="n"/>
+      <c r="O4" s="9" t="n"/>
+      <c r="P4" s="9">
+        <f>IF(COUNT(D4:I4)=0,"",SUM(D4:I4))</f>
+        <v/>
+      </c>
+      <c r="Q4" s="9">
+        <f>IF(COUNT(J4:O4)=0,"",SUM(J4:O4))</f>
+        <v/>
+      </c>
+      <c r="R4" s="9">
+        <f>IF(COUNT(P4:Q4)=0,"",ROUND(AVERAGE(P4:Q4),1))</f>
+        <v/>
+      </c>
+      <c r="S4" s="9" t="n"/>
+      <c r="T4" s="9" t="n"/>
+      <c r="U4" s="9" t="n"/>
+      <c r="V4" s="9" t="n"/>
     </row>
     <row r="5" ht="19" customHeight="1">
       <c r="A5" s="6" t="n">
@@ -3577,14 +5141,32 @@
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7">
-        <f>IF(COUNT(D5:E5)=0,"",ROUND(AVERAGE(D5:E5),1))</f>
-        <v/>
-      </c>
+      <c r="F5" s="7" t="n"/>
       <c r="G5" s="7" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
       <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="7" t="n"/>
+      <c r="M5" s="7" t="n"/>
+      <c r="N5" s="7" t="n"/>
+      <c r="O5" s="7" t="n"/>
+      <c r="P5" s="7">
+        <f>IF(COUNT(D5:I5)=0,"",SUM(D5:I5))</f>
+        <v/>
+      </c>
+      <c r="Q5" s="7">
+        <f>IF(COUNT(J5:O5)=0,"",SUM(J5:O5))</f>
+        <v/>
+      </c>
+      <c r="R5" s="7">
+        <f>IF(COUNT(P5:Q5)=0,"",ROUND(AVERAGE(P5:Q5),1))</f>
+        <v/>
+      </c>
+      <c r="S5" s="7" t="n"/>
+      <c r="T5" s="7" t="n"/>
+      <c r="U5" s="7" t="n"/>
+      <c r="V5" s="7" t="n"/>
     </row>
     <row r="6" ht="19" customHeight="1">
       <c r="A6" s="8" t="n">
@@ -3594,14 +5176,32 @@
       <c r="C6" s="9" t="n"/>
       <c r="D6" s="9" t="n"/>
       <c r="E6" s="9" t="n"/>
-      <c r="F6" s="9">
-        <f>IF(COUNT(D6:E6)=0,"",ROUND(AVERAGE(D6:E6),1))</f>
-        <v/>
-      </c>
+      <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
       <c r="H6" s="9" t="n"/>
       <c r="I6" s="9" t="n"/>
       <c r="J6" s="9" t="n"/>
+      <c r="K6" s="9" t="n"/>
+      <c r="L6" s="9" t="n"/>
+      <c r="M6" s="9" t="n"/>
+      <c r="N6" s="9" t="n"/>
+      <c r="O6" s="9" t="n"/>
+      <c r="P6" s="9">
+        <f>IF(COUNT(D6:I6)=0,"",SUM(D6:I6))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="9">
+        <f>IF(COUNT(J6:O6)=0,"",SUM(J6:O6))</f>
+        <v/>
+      </c>
+      <c r="R6" s="9">
+        <f>IF(COUNT(P6:Q6)=0,"",ROUND(AVERAGE(P6:Q6),1))</f>
+        <v/>
+      </c>
+      <c r="S6" s="9" t="n"/>
+      <c r="T6" s="9" t="n"/>
+      <c r="U6" s="9" t="n"/>
+      <c r="V6" s="9" t="n"/>
     </row>
     <row r="7" ht="19" customHeight="1">
       <c r="A7" s="6" t="n">
@@ -3611,14 +5211,32 @@
       <c r="C7" s="7" t="n"/>
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7">
-        <f>IF(COUNT(D7:E7)=0,"",ROUND(AVERAGE(D7:E7),1))</f>
-        <v/>
-      </c>
+      <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
       <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="7" t="n"/>
+      <c r="M7" s="7" t="n"/>
+      <c r="N7" s="7" t="n"/>
+      <c r="O7" s="7" t="n"/>
+      <c r="P7" s="7">
+        <f>IF(COUNT(D7:I7)=0,"",SUM(D7:I7))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="7">
+        <f>IF(COUNT(J7:O7)=0,"",SUM(J7:O7))</f>
+        <v/>
+      </c>
+      <c r="R7" s="7">
+        <f>IF(COUNT(P7:Q7)=0,"",ROUND(AVERAGE(P7:Q7),1))</f>
+        <v/>
+      </c>
+      <c r="S7" s="7" t="n"/>
+      <c r="T7" s="7" t="n"/>
+      <c r="U7" s="7" t="n"/>
+      <c r="V7" s="7" t="n"/>
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="8" t="n">
@@ -3628,14 +5246,32 @@
       <c r="C8" s="9" t="n"/>
       <c r="D8" s="9" t="n"/>
       <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9">
-        <f>IF(COUNT(D8:E8)=0,"",ROUND(AVERAGE(D8:E8),1))</f>
-        <v/>
-      </c>
+      <c r="F8" s="9" t="n"/>
       <c r="G8" s="9" t="n"/>
       <c r="H8" s="9" t="n"/>
       <c r="I8" s="9" t="n"/>
       <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" s="9" t="n"/>
+      <c r="M8" s="9" t="n"/>
+      <c r="N8" s="9" t="n"/>
+      <c r="O8" s="9" t="n"/>
+      <c r="P8" s="9">
+        <f>IF(COUNT(D8:I8)=0,"",SUM(D8:I8))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="9">
+        <f>IF(COUNT(J8:O8)=0,"",SUM(J8:O8))</f>
+        <v/>
+      </c>
+      <c r="R8" s="9">
+        <f>IF(COUNT(P8:Q8)=0,"",ROUND(AVERAGE(P8:Q8),1))</f>
+        <v/>
+      </c>
+      <c r="S8" s="9" t="n"/>
+      <c r="T8" s="9" t="n"/>
+      <c r="U8" s="9" t="n"/>
+      <c r="V8" s="9" t="n"/>
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" s="6" t="n">
@@ -3645,14 +5281,32 @@
       <c r="C9" s="7" t="n"/>
       <c r="D9" s="7" t="n"/>
       <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7">
-        <f>IF(COUNT(D9:E9)=0,"",ROUND(AVERAGE(D9:E9),1))</f>
-        <v/>
-      </c>
+      <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n"/>
       <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
+      <c r="N9" s="7" t="n"/>
+      <c r="O9" s="7" t="n"/>
+      <c r="P9" s="7">
+        <f>IF(COUNT(D9:I9)=0,"",SUM(D9:I9))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="7">
+        <f>IF(COUNT(J9:O9)=0,"",SUM(J9:O9))</f>
+        <v/>
+      </c>
+      <c r="R9" s="7">
+        <f>IF(COUNT(P9:Q9)=0,"",ROUND(AVERAGE(P9:Q9),1))</f>
+        <v/>
+      </c>
+      <c r="S9" s="7" t="n"/>
+      <c r="T9" s="7" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="8" t="n">
@@ -3662,14 +5316,32 @@
       <c r="C10" s="9" t="n"/>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9">
-        <f>IF(COUNT(D10:E10)=0,"",ROUND(AVERAGE(D10:E10),1))</f>
-        <v/>
-      </c>
+      <c r="F10" s="9" t="n"/>
       <c r="G10" s="9" t="n"/>
       <c r="H10" s="9" t="n"/>
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="9" t="n"/>
+      <c r="K10" s="9" t="n"/>
+      <c r="L10" s="9" t="n"/>
+      <c r="M10" s="9" t="n"/>
+      <c r="N10" s="9" t="n"/>
+      <c r="O10" s="9" t="n"/>
+      <c r="P10" s="9">
+        <f>IF(COUNT(D10:I10)=0,"",SUM(D10:I10))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="9">
+        <f>IF(COUNT(J10:O10)=0,"",SUM(J10:O10))</f>
+        <v/>
+      </c>
+      <c r="R10" s="9">
+        <f>IF(COUNT(P10:Q10)=0,"",ROUND(AVERAGE(P10:Q10),1))</f>
+        <v/>
+      </c>
+      <c r="S10" s="9" t="n"/>
+      <c r="T10" s="9" t="n"/>
+      <c r="U10" s="9" t="n"/>
+      <c r="V10" s="9" t="n"/>
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="6" t="n">
@@ -3679,14 +5351,32 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7">
-        <f>IF(COUNT(D11:E11)=0,"",ROUND(AVERAGE(D11:E11),1))</f>
-        <v/>
-      </c>
+      <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
       <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="7" t="n"/>
+      <c r="M11" s="7" t="n"/>
+      <c r="N11" s="7" t="n"/>
+      <c r="O11" s="7" t="n"/>
+      <c r="P11" s="7">
+        <f>IF(COUNT(D11:I11)=0,"",SUM(D11:I11))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="7">
+        <f>IF(COUNT(J11:O11)=0,"",SUM(J11:O11))</f>
+        <v/>
+      </c>
+      <c r="R11" s="7">
+        <f>IF(COUNT(P11:Q11)=0,"",ROUND(AVERAGE(P11:Q11),1))</f>
+        <v/>
+      </c>
+      <c r="S11" s="7" t="n"/>
+      <c r="T11" s="7" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="7" t="n"/>
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="8" t="n">
@@ -3696,14 +5386,32 @@
       <c r="C12" s="9" t="n"/>
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9">
-        <f>IF(COUNT(D12:E12)=0,"",ROUND(AVERAGE(D12:E12),1))</f>
-        <v/>
-      </c>
+      <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n"/>
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="9" t="n"/>
       <c r="J12" s="9" t="n"/>
+      <c r="K12" s="9" t="n"/>
+      <c r="L12" s="9" t="n"/>
+      <c r="M12" s="9" t="n"/>
+      <c r="N12" s="9" t="n"/>
+      <c r="O12" s="9" t="n"/>
+      <c r="P12" s="9">
+        <f>IF(COUNT(D12:I12)=0,"",SUM(D12:I12))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="9">
+        <f>IF(COUNT(J12:O12)=0,"",SUM(J12:O12))</f>
+        <v/>
+      </c>
+      <c r="R12" s="9">
+        <f>IF(COUNT(P12:Q12)=0,"",ROUND(AVERAGE(P12:Q12),1))</f>
+        <v/>
+      </c>
+      <c r="S12" s="9" t="n"/>
+      <c r="T12" s="9" t="n"/>
+      <c r="U12" s="9" t="n"/>
+      <c r="V12" s="9" t="n"/>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="6" t="n">
@@ -3713,14 +5421,32 @@
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7">
-        <f>IF(COUNT(D13:E13)=0,"",ROUND(AVERAGE(D13:E13),1))</f>
-        <v/>
-      </c>
+      <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="7" t="n"/>
       <c r="J13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="7" t="n"/>
+      <c r="M13" s="7" t="n"/>
+      <c r="N13" s="7" t="n"/>
+      <c r="O13" s="7" t="n"/>
+      <c r="P13" s="7">
+        <f>IF(COUNT(D13:I13)=0,"",SUM(D13:I13))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="7">
+        <f>IF(COUNT(J13:O13)=0,"",SUM(J13:O13))</f>
+        <v/>
+      </c>
+      <c r="R13" s="7">
+        <f>IF(COUNT(P13:Q13)=0,"",ROUND(AVERAGE(P13:Q13),1))</f>
+        <v/>
+      </c>
+      <c r="S13" s="7" t="n"/>
+      <c r="T13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="8" t="n">
@@ -3730,14 +5456,32 @@
       <c r="C14" s="9" t="n"/>
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9">
-        <f>IF(COUNT(D14:E14)=0,"",ROUND(AVERAGE(D14:E14),1))</f>
-        <v/>
-      </c>
+      <c r="F14" s="9" t="n"/>
       <c r="G14" s="9" t="n"/>
       <c r="H14" s="9" t="n"/>
       <c r="I14" s="9" t="n"/>
       <c r="J14" s="9" t="n"/>
+      <c r="K14" s="9" t="n"/>
+      <c r="L14" s="9" t="n"/>
+      <c r="M14" s="9" t="n"/>
+      <c r="N14" s="9" t="n"/>
+      <c r="O14" s="9" t="n"/>
+      <c r="P14" s="9">
+        <f>IF(COUNT(D14:I14)=0,"",SUM(D14:I14))</f>
+        <v/>
+      </c>
+      <c r="Q14" s="9">
+        <f>IF(COUNT(J14:O14)=0,"",SUM(J14:O14))</f>
+        <v/>
+      </c>
+      <c r="R14" s="9">
+        <f>IF(COUNT(P14:Q14)=0,"",ROUND(AVERAGE(P14:Q14),1))</f>
+        <v/>
+      </c>
+      <c r="S14" s="9" t="n"/>
+      <c r="T14" s="9" t="n"/>
+      <c r="U14" s="9" t="n"/>
+      <c r="V14" s="9" t="n"/>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="6" t="n">
@@ -3747,14 +5491,32 @@
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="7" t="n"/>
       <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7">
-        <f>IF(COUNT(D15:E15)=0,"",ROUND(AVERAGE(D15:E15),1))</f>
-        <v/>
-      </c>
+      <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="7" t="n"/>
       <c r="I15" s="7" t="n"/>
       <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
+      <c r="N15" s="7" t="n"/>
+      <c r="O15" s="7" t="n"/>
+      <c r="P15" s="7">
+        <f>IF(COUNT(D15:I15)=0,"",SUM(D15:I15))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="7">
+        <f>IF(COUNT(J15:O15)=0,"",SUM(J15:O15))</f>
+        <v/>
+      </c>
+      <c r="R15" s="7">
+        <f>IF(COUNT(P15:Q15)=0,"",ROUND(AVERAGE(P15:Q15),1))</f>
+        <v/>
+      </c>
+      <c r="S15" s="7" t="n"/>
+      <c r="T15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="8" t="n">
@@ -3764,14 +5526,32 @@
       <c r="C16" s="9" t="n"/>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9">
-        <f>IF(COUNT(D16:E16)=0,"",ROUND(AVERAGE(D16:E16),1))</f>
-        <v/>
-      </c>
+      <c r="F16" s="9" t="n"/>
       <c r="G16" s="9" t="n"/>
       <c r="H16" s="9" t="n"/>
       <c r="I16" s="9" t="n"/>
       <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
+      <c r="L16" s="9" t="n"/>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="9" t="n"/>
+      <c r="O16" s="9" t="n"/>
+      <c r="P16" s="9">
+        <f>IF(COUNT(D16:I16)=0,"",SUM(D16:I16))</f>
+        <v/>
+      </c>
+      <c r="Q16" s="9">
+        <f>IF(COUNT(J16:O16)=0,"",SUM(J16:O16))</f>
+        <v/>
+      </c>
+      <c r="R16" s="9">
+        <f>IF(COUNT(P16:Q16)=0,"",ROUND(AVERAGE(P16:Q16),1))</f>
+        <v/>
+      </c>
+      <c r="S16" s="9" t="n"/>
+      <c r="T16" s="9" t="n"/>
+      <c r="U16" s="9" t="n"/>
+      <c r="V16" s="9" t="n"/>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="6" t="n">
@@ -3781,14 +5561,32 @@
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7">
-        <f>IF(COUNT(D17:E17)=0,"",ROUND(AVERAGE(D17:E17),1))</f>
-        <v/>
-      </c>
+      <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
       <c r="H17" s="7" t="n"/>
       <c r="I17" s="7" t="n"/>
       <c r="J17" s="7" t="n"/>
+      <c r="K17" s="7" t="n"/>
+      <c r="L17" s="7" t="n"/>
+      <c r="M17" s="7" t="n"/>
+      <c r="N17" s="7" t="n"/>
+      <c r="O17" s="7" t="n"/>
+      <c r="P17" s="7">
+        <f>IF(COUNT(D17:I17)=0,"",SUM(D17:I17))</f>
+        <v/>
+      </c>
+      <c r="Q17" s="7">
+        <f>IF(COUNT(J17:O17)=0,"",SUM(J17:O17))</f>
+        <v/>
+      </c>
+      <c r="R17" s="7">
+        <f>IF(COUNT(P17:Q17)=0,"",ROUND(AVERAGE(P17:Q17),1))</f>
+        <v/>
+      </c>
+      <c r="S17" s="7" t="n"/>
+      <c r="T17" s="7" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="8" t="n">
@@ -3798,14 +5596,32 @@
       <c r="C18" s="9" t="n"/>
       <c r="D18" s="9" t="n"/>
       <c r="E18" s="9" t="n"/>
-      <c r="F18" s="9">
-        <f>IF(COUNT(D18:E18)=0,"",ROUND(AVERAGE(D18:E18),1))</f>
-        <v/>
-      </c>
+      <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n"/>
       <c r="H18" s="9" t="n"/>
       <c r="I18" s="9" t="n"/>
       <c r="J18" s="9" t="n"/>
+      <c r="K18" s="9" t="n"/>
+      <c r="L18" s="9" t="n"/>
+      <c r="M18" s="9" t="n"/>
+      <c r="N18" s="9" t="n"/>
+      <c r="O18" s="9" t="n"/>
+      <c r="P18" s="9">
+        <f>IF(COUNT(D18:I18)=0,"",SUM(D18:I18))</f>
+        <v/>
+      </c>
+      <c r="Q18" s="9">
+        <f>IF(COUNT(J18:O18)=0,"",SUM(J18:O18))</f>
+        <v/>
+      </c>
+      <c r="R18" s="9">
+        <f>IF(COUNT(P18:Q18)=0,"",ROUND(AVERAGE(P18:Q18),1))</f>
+        <v/>
+      </c>
+      <c r="S18" s="9" t="n"/>
+      <c r="T18" s="9" t="n"/>
+      <c r="U18" s="9" t="n"/>
+      <c r="V18" s="9" t="n"/>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="6" t="n">
@@ -3815,14 +5631,32 @@
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7">
-        <f>IF(COUNT(D19:E19)=0,"",ROUND(AVERAGE(D19:E19),1))</f>
-        <v/>
-      </c>
+      <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="7" t="n"/>
       <c r="J19" s="7" t="n"/>
+      <c r="K19" s="7" t="n"/>
+      <c r="L19" s="7" t="n"/>
+      <c r="M19" s="7" t="n"/>
+      <c r="N19" s="7" t="n"/>
+      <c r="O19" s="7" t="n"/>
+      <c r="P19" s="7">
+        <f>IF(COUNT(D19:I19)=0,"",SUM(D19:I19))</f>
+        <v/>
+      </c>
+      <c r="Q19" s="7">
+        <f>IF(COUNT(J19:O19)=0,"",SUM(J19:O19))</f>
+        <v/>
+      </c>
+      <c r="R19" s="7">
+        <f>IF(COUNT(P19:Q19)=0,"",ROUND(AVERAGE(P19:Q19),1))</f>
+        <v/>
+      </c>
+      <c r="S19" s="7" t="n"/>
+      <c r="T19" s="7" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="8" t="n">
@@ -3832,14 +5666,32 @@
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9">
-        <f>IF(COUNT(D20:E20)=0,"",ROUND(AVERAGE(D20:E20),1))</f>
-        <v/>
-      </c>
+      <c r="F20" s="9" t="n"/>
       <c r="G20" s="9" t="n"/>
       <c r="H20" s="9" t="n"/>
       <c r="I20" s="9" t="n"/>
       <c r="J20" s="9" t="n"/>
+      <c r="K20" s="9" t="n"/>
+      <c r="L20" s="9" t="n"/>
+      <c r="M20" s="9" t="n"/>
+      <c r="N20" s="9" t="n"/>
+      <c r="O20" s="9" t="n"/>
+      <c r="P20" s="9">
+        <f>IF(COUNT(D20:I20)=0,"",SUM(D20:I20))</f>
+        <v/>
+      </c>
+      <c r="Q20" s="9">
+        <f>IF(COUNT(J20:O20)=0,"",SUM(J20:O20))</f>
+        <v/>
+      </c>
+      <c r="R20" s="9">
+        <f>IF(COUNT(P20:Q20)=0,"",ROUND(AVERAGE(P20:Q20),1))</f>
+        <v/>
+      </c>
+      <c r="S20" s="9" t="n"/>
+      <c r="T20" s="9" t="n"/>
+      <c r="U20" s="9" t="n"/>
+      <c r="V20" s="9" t="n"/>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="6" t="n">
@@ -3849,14 +5701,32 @@
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7">
-        <f>IF(COUNT(D21:E21)=0,"",ROUND(AVERAGE(D21:E21),1))</f>
-        <v/>
-      </c>
+      <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="7" t="n"/>
       <c r="I21" s="7" t="n"/>
       <c r="J21" s="7" t="n"/>
+      <c r="K21" s="7" t="n"/>
+      <c r="L21" s="7" t="n"/>
+      <c r="M21" s="7" t="n"/>
+      <c r="N21" s="7" t="n"/>
+      <c r="O21" s="7" t="n"/>
+      <c r="P21" s="7">
+        <f>IF(COUNT(D21:I21)=0,"",SUM(D21:I21))</f>
+        <v/>
+      </c>
+      <c r="Q21" s="7">
+        <f>IF(COUNT(J21:O21)=0,"",SUM(J21:O21))</f>
+        <v/>
+      </c>
+      <c r="R21" s="7">
+        <f>IF(COUNT(P21:Q21)=0,"",ROUND(AVERAGE(P21:Q21),1))</f>
+        <v/>
+      </c>
+      <c r="S21" s="7" t="n"/>
+      <c r="T21" s="7" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="8" t="n">
@@ -3866,14 +5736,32 @@
       <c r="C22" s="9" t="n"/>
       <c r="D22" s="9" t="n"/>
       <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9">
-        <f>IF(COUNT(D22:E22)=0,"",ROUND(AVERAGE(D22:E22),1))</f>
-        <v/>
-      </c>
+      <c r="F22" s="9" t="n"/>
       <c r="G22" s="9" t="n"/>
       <c r="H22" s="9" t="n"/>
       <c r="I22" s="9" t="n"/>
       <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
+      <c r="L22" s="9" t="n"/>
+      <c r="M22" s="9" t="n"/>
+      <c r="N22" s="9" t="n"/>
+      <c r="O22" s="9" t="n"/>
+      <c r="P22" s="9">
+        <f>IF(COUNT(D22:I22)=0,"",SUM(D22:I22))</f>
+        <v/>
+      </c>
+      <c r="Q22" s="9">
+        <f>IF(COUNT(J22:O22)=0,"",SUM(J22:O22))</f>
+        <v/>
+      </c>
+      <c r="R22" s="9">
+        <f>IF(COUNT(P22:Q22)=0,"",ROUND(AVERAGE(P22:Q22),1))</f>
+        <v/>
+      </c>
+      <c r="S22" s="9" t="n"/>
+      <c r="T22" s="9" t="n"/>
+      <c r="U22" s="9" t="n"/>
+      <c r="V22" s="9" t="n"/>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="6" t="n">
@@ -3883,14 +5771,32 @@
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7">
-        <f>IF(COUNT(D23:E23)=0,"",ROUND(AVERAGE(D23:E23),1))</f>
-        <v/>
-      </c>
+      <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
       <c r="I23" s="7" t="n"/>
       <c r="J23" s="7" t="n"/>
+      <c r="K23" s="7" t="n"/>
+      <c r="L23" s="7" t="n"/>
+      <c r="M23" s="7" t="n"/>
+      <c r="N23" s="7" t="n"/>
+      <c r="O23" s="7" t="n"/>
+      <c r="P23" s="7">
+        <f>IF(COUNT(D23:I23)=0,"",SUM(D23:I23))</f>
+        <v/>
+      </c>
+      <c r="Q23" s="7">
+        <f>IF(COUNT(J23:O23)=0,"",SUM(J23:O23))</f>
+        <v/>
+      </c>
+      <c r="R23" s="7">
+        <f>IF(COUNT(P23:Q23)=0,"",ROUND(AVERAGE(P23:Q23),1))</f>
+        <v/>
+      </c>
+      <c r="S23" s="7" t="n"/>
+      <c r="T23" s="7" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="7" t="n"/>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="8" t="n">
@@ -3900,14 +5806,32 @@
       <c r="C24" s="9" t="n"/>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9">
-        <f>IF(COUNT(D24:E24)=0,"",ROUND(AVERAGE(D24:E24),1))</f>
-        <v/>
-      </c>
+      <c r="F24" s="9" t="n"/>
       <c r="G24" s="9" t="n"/>
       <c r="H24" s="9" t="n"/>
       <c r="I24" s="9" t="n"/>
       <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
+      <c r="L24" s="9" t="n"/>
+      <c r="M24" s="9" t="n"/>
+      <c r="N24" s="9" t="n"/>
+      <c r="O24" s="9" t="n"/>
+      <c r="P24" s="9">
+        <f>IF(COUNT(D24:I24)=0,"",SUM(D24:I24))</f>
+        <v/>
+      </c>
+      <c r="Q24" s="9">
+        <f>IF(COUNT(J24:O24)=0,"",SUM(J24:O24))</f>
+        <v/>
+      </c>
+      <c r="R24" s="9">
+        <f>IF(COUNT(P24:Q24)=0,"",ROUND(AVERAGE(P24:Q24),1))</f>
+        <v/>
+      </c>
+      <c r="S24" s="9" t="n"/>
+      <c r="T24" s="9" t="n"/>
+      <c r="U24" s="9" t="n"/>
+      <c r="V24" s="9" t="n"/>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="6" t="n">
@@ -3917,14 +5841,32 @@
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7">
-        <f>IF(COUNT(D25:E25)=0,"",ROUND(AVERAGE(D25:E25),1))</f>
-        <v/>
-      </c>
+      <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
       <c r="I25" s="7" t="n"/>
       <c r="J25" s="7" t="n"/>
+      <c r="K25" s="7" t="n"/>
+      <c r="L25" s="7" t="n"/>
+      <c r="M25" s="7" t="n"/>
+      <c r="N25" s="7" t="n"/>
+      <c r="O25" s="7" t="n"/>
+      <c r="P25" s="7">
+        <f>IF(COUNT(D25:I25)=0,"",SUM(D25:I25))</f>
+        <v/>
+      </c>
+      <c r="Q25" s="7">
+        <f>IF(COUNT(J25:O25)=0,"",SUM(J25:O25))</f>
+        <v/>
+      </c>
+      <c r="R25" s="7">
+        <f>IF(COUNT(P25:Q25)=0,"",ROUND(AVERAGE(P25:Q25),1))</f>
+        <v/>
+      </c>
+      <c r="S25" s="7" t="n"/>
+      <c r="T25" s="7" t="n"/>
+      <c r="U25" s="7" t="n"/>
+      <c r="V25" s="7" t="n"/>
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="8" t="n">
@@ -3934,14 +5876,32 @@
       <c r="C26" s="9" t="n"/>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9">
-        <f>IF(COUNT(D26:E26)=0,"",ROUND(AVERAGE(D26:E26),1))</f>
-        <v/>
-      </c>
+      <c r="F26" s="9" t="n"/>
       <c r="G26" s="9" t="n"/>
       <c r="H26" s="9" t="n"/>
       <c r="I26" s="9" t="n"/>
       <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
+      <c r="L26" s="9" t="n"/>
+      <c r="M26" s="9" t="n"/>
+      <c r="N26" s="9" t="n"/>
+      <c r="O26" s="9" t="n"/>
+      <c r="P26" s="9">
+        <f>IF(COUNT(D26:I26)=0,"",SUM(D26:I26))</f>
+        <v/>
+      </c>
+      <c r="Q26" s="9">
+        <f>IF(COUNT(J26:O26)=0,"",SUM(J26:O26))</f>
+        <v/>
+      </c>
+      <c r="R26" s="9">
+        <f>IF(COUNT(P26:Q26)=0,"",ROUND(AVERAGE(P26:Q26),1))</f>
+        <v/>
+      </c>
+      <c r="S26" s="9" t="n"/>
+      <c r="T26" s="9" t="n"/>
+      <c r="U26" s="9" t="n"/>
+      <c r="V26" s="9" t="n"/>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="6" t="n">
@@ -3951,14 +5911,32 @@
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7">
-        <f>IF(COUNT(D27:E27)=0,"",ROUND(AVERAGE(D27:E27),1))</f>
-        <v/>
-      </c>
+      <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="7" t="n"/>
       <c r="I27" s="7" t="n"/>
       <c r="J27" s="7" t="n"/>
+      <c r="K27" s="7" t="n"/>
+      <c r="L27" s="7" t="n"/>
+      <c r="M27" s="7" t="n"/>
+      <c r="N27" s="7" t="n"/>
+      <c r="O27" s="7" t="n"/>
+      <c r="P27" s="7">
+        <f>IF(COUNT(D27:I27)=0,"",SUM(D27:I27))</f>
+        <v/>
+      </c>
+      <c r="Q27" s="7">
+        <f>IF(COUNT(J27:O27)=0,"",SUM(J27:O27))</f>
+        <v/>
+      </c>
+      <c r="R27" s="7">
+        <f>IF(COUNT(P27:Q27)=0,"",ROUND(AVERAGE(P27:Q27),1))</f>
+        <v/>
+      </c>
+      <c r="S27" s="7" t="n"/>
+      <c r="T27" s="7" t="n"/>
+      <c r="U27" s="7" t="n"/>
+      <c r="V27" s="7" t="n"/>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="8" t="n">
@@ -3968,14 +5946,32 @@
       <c r="C28" s="9" t="n"/>
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9">
-        <f>IF(COUNT(D28:E28)=0,"",ROUND(AVERAGE(D28:E28),1))</f>
-        <v/>
-      </c>
+      <c r="F28" s="9" t="n"/>
       <c r="G28" s="9" t="n"/>
       <c r="H28" s="9" t="n"/>
       <c r="I28" s="9" t="n"/>
       <c r="J28" s="9" t="n"/>
+      <c r="K28" s="9" t="n"/>
+      <c r="L28" s="9" t="n"/>
+      <c r="M28" s="9" t="n"/>
+      <c r="N28" s="9" t="n"/>
+      <c r="O28" s="9" t="n"/>
+      <c r="P28" s="9">
+        <f>IF(COUNT(D28:I28)=0,"",SUM(D28:I28))</f>
+        <v/>
+      </c>
+      <c r="Q28" s="9">
+        <f>IF(COUNT(J28:O28)=0,"",SUM(J28:O28))</f>
+        <v/>
+      </c>
+      <c r="R28" s="9">
+        <f>IF(COUNT(P28:Q28)=0,"",ROUND(AVERAGE(P28:Q28),1))</f>
+        <v/>
+      </c>
+      <c r="S28" s="9" t="n"/>
+      <c r="T28" s="9" t="n"/>
+      <c r="U28" s="9" t="n"/>
+      <c r="V28" s="9" t="n"/>
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="6" t="n">
@@ -3985,14 +5981,32 @@
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7">
-        <f>IF(COUNT(D29:E29)=0,"",ROUND(AVERAGE(D29:E29),1))</f>
-        <v/>
-      </c>
+      <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
       <c r="H29" s="7" t="n"/>
       <c r="I29" s="7" t="n"/>
       <c r="J29" s="7" t="n"/>
+      <c r="K29" s="7" t="n"/>
+      <c r="L29" s="7" t="n"/>
+      <c r="M29" s="7" t="n"/>
+      <c r="N29" s="7" t="n"/>
+      <c r="O29" s="7" t="n"/>
+      <c r="P29" s="7">
+        <f>IF(COUNT(D29:I29)=0,"",SUM(D29:I29))</f>
+        <v/>
+      </c>
+      <c r="Q29" s="7">
+        <f>IF(COUNT(J29:O29)=0,"",SUM(J29:O29))</f>
+        <v/>
+      </c>
+      <c r="R29" s="7">
+        <f>IF(COUNT(P29:Q29)=0,"",ROUND(AVERAGE(P29:Q29),1))</f>
+        <v/>
+      </c>
+      <c r="S29" s="7" t="n"/>
+      <c r="T29" s="7" t="n"/>
+      <c r="U29" s="7" t="n"/>
+      <c r="V29" s="7" t="n"/>
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="8" t="n">
@@ -4002,14 +6016,32 @@
       <c r="C30" s="9" t="n"/>
       <c r="D30" s="9" t="n"/>
       <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9">
-        <f>IF(COUNT(D30:E30)=0,"",ROUND(AVERAGE(D30:E30),1))</f>
-        <v/>
-      </c>
+      <c r="F30" s="9" t="n"/>
       <c r="G30" s="9" t="n"/>
       <c r="H30" s="9" t="n"/>
       <c r="I30" s="9" t="n"/>
       <c r="J30" s="9" t="n"/>
+      <c r="K30" s="9" t="n"/>
+      <c r="L30" s="9" t="n"/>
+      <c r="M30" s="9" t="n"/>
+      <c r="N30" s="9" t="n"/>
+      <c r="O30" s="9" t="n"/>
+      <c r="P30" s="9">
+        <f>IF(COUNT(D30:I30)=0,"",SUM(D30:I30))</f>
+        <v/>
+      </c>
+      <c r="Q30" s="9">
+        <f>IF(COUNT(J30:O30)=0,"",SUM(J30:O30))</f>
+        <v/>
+      </c>
+      <c r="R30" s="9">
+        <f>IF(COUNT(P30:Q30)=0,"",ROUND(AVERAGE(P30:Q30),1))</f>
+        <v/>
+      </c>
+      <c r="S30" s="9" t="n"/>
+      <c r="T30" s="9" t="n"/>
+      <c r="U30" s="9" t="n"/>
+      <c r="V30" s="9" t="n"/>
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="6" t="n">
@@ -4019,14 +6051,32 @@
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7">
-        <f>IF(COUNT(D31:E31)=0,"",ROUND(AVERAGE(D31:E31),1))</f>
-        <v/>
-      </c>
+      <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="7" t="n"/>
       <c r="I31" s="7" t="n"/>
       <c r="J31" s="7" t="n"/>
+      <c r="K31" s="7" t="n"/>
+      <c r="L31" s="7" t="n"/>
+      <c r="M31" s="7" t="n"/>
+      <c r="N31" s="7" t="n"/>
+      <c r="O31" s="7" t="n"/>
+      <c r="P31" s="7">
+        <f>IF(COUNT(D31:I31)=0,"",SUM(D31:I31))</f>
+        <v/>
+      </c>
+      <c r="Q31" s="7">
+        <f>IF(COUNT(J31:O31)=0,"",SUM(J31:O31))</f>
+        <v/>
+      </c>
+      <c r="R31" s="7">
+        <f>IF(COUNT(P31:Q31)=0,"",ROUND(AVERAGE(P31:Q31),1))</f>
+        <v/>
+      </c>
+      <c r="S31" s="7" t="n"/>
+      <c r="T31" s="7" t="n"/>
+      <c r="U31" s="7" t="n"/>
+      <c r="V31" s="7" t="n"/>
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="8" t="n">
@@ -4036,14 +6086,32 @@
       <c r="C32" s="9" t="n"/>
       <c r="D32" s="9" t="n"/>
       <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9">
-        <f>IF(COUNT(D32:E32)=0,"",ROUND(AVERAGE(D32:E32),1))</f>
-        <v/>
-      </c>
+      <c r="F32" s="9" t="n"/>
       <c r="G32" s="9" t="n"/>
       <c r="H32" s="9" t="n"/>
       <c r="I32" s="9" t="n"/>
       <c r="J32" s="9" t="n"/>
+      <c r="K32" s="9" t="n"/>
+      <c r="L32" s="9" t="n"/>
+      <c r="M32" s="9" t="n"/>
+      <c r="N32" s="9" t="n"/>
+      <c r="O32" s="9" t="n"/>
+      <c r="P32" s="9">
+        <f>IF(COUNT(D32:I32)=0,"",SUM(D32:I32))</f>
+        <v/>
+      </c>
+      <c r="Q32" s="9">
+        <f>IF(COUNT(J32:O32)=0,"",SUM(J32:O32))</f>
+        <v/>
+      </c>
+      <c r="R32" s="9">
+        <f>IF(COUNT(P32:Q32)=0,"",ROUND(AVERAGE(P32:Q32),1))</f>
+        <v/>
+      </c>
+      <c r="S32" s="9" t="n"/>
+      <c r="T32" s="9" t="n"/>
+      <c r="U32" s="9" t="n"/>
+      <c r="V32" s="9" t="n"/>
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="6" t="n">
@@ -4053,14 +6121,32 @@
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7">
-        <f>IF(COUNT(D33:E33)=0,"",ROUND(AVERAGE(D33:E33),1))</f>
-        <v/>
-      </c>
+      <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
       <c r="H33" s="7" t="n"/>
       <c r="I33" s="7" t="n"/>
       <c r="J33" s="7" t="n"/>
+      <c r="K33" s="7" t="n"/>
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
+      <c r="N33" s="7" t="n"/>
+      <c r="O33" s="7" t="n"/>
+      <c r="P33" s="7">
+        <f>IF(COUNT(D33:I33)=0,"",SUM(D33:I33))</f>
+        <v/>
+      </c>
+      <c r="Q33" s="7">
+        <f>IF(COUNT(J33:O33)=0,"",SUM(J33:O33))</f>
+        <v/>
+      </c>
+      <c r="R33" s="7">
+        <f>IF(COUNT(P33:Q33)=0,"",ROUND(AVERAGE(P33:Q33),1))</f>
+        <v/>
+      </c>
+      <c r="S33" s="7" t="n"/>
+      <c r="T33" s="7" t="n"/>
+      <c r="U33" s="7" t="n"/>
+      <c r="V33" s="7" t="n"/>
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="8" t="n">
@@ -4070,14 +6156,32 @@
       <c r="C34" s="9" t="n"/>
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
-      <c r="F34" s="9">
-        <f>IF(COUNT(D34:E34)=0,"",ROUND(AVERAGE(D34:E34),1))</f>
-        <v/>
-      </c>
+      <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n"/>
       <c r="H34" s="9" t="n"/>
       <c r="I34" s="9" t="n"/>
       <c r="J34" s="9" t="n"/>
+      <c r="K34" s="9" t="n"/>
+      <c r="L34" s="9" t="n"/>
+      <c r="M34" s="9" t="n"/>
+      <c r="N34" s="9" t="n"/>
+      <c r="O34" s="9" t="n"/>
+      <c r="P34" s="9">
+        <f>IF(COUNT(D34:I34)=0,"",SUM(D34:I34))</f>
+        <v/>
+      </c>
+      <c r="Q34" s="9">
+        <f>IF(COUNT(J34:O34)=0,"",SUM(J34:O34))</f>
+        <v/>
+      </c>
+      <c r="R34" s="9">
+        <f>IF(COUNT(P34:Q34)=0,"",ROUND(AVERAGE(P34:Q34),1))</f>
+        <v/>
+      </c>
+      <c r="S34" s="9" t="n"/>
+      <c r="T34" s="9" t="n"/>
+      <c r="U34" s="9" t="n"/>
+      <c r="V34" s="9" t="n"/>
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="6" t="n">
@@ -4087,14 +6191,32 @@
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
-      <c r="F35" s="7">
-        <f>IF(COUNT(D35:E35)=0,"",ROUND(AVERAGE(D35:E35),1))</f>
-        <v/>
-      </c>
+      <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
       <c r="H35" s="7" t="n"/>
       <c r="I35" s="7" t="n"/>
       <c r="J35" s="7" t="n"/>
+      <c r="K35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
+      <c r="N35" s="7" t="n"/>
+      <c r="O35" s="7" t="n"/>
+      <c r="P35" s="7">
+        <f>IF(COUNT(D35:I35)=0,"",SUM(D35:I35))</f>
+        <v/>
+      </c>
+      <c r="Q35" s="7">
+        <f>IF(COUNT(J35:O35)=0,"",SUM(J35:O35))</f>
+        <v/>
+      </c>
+      <c r="R35" s="7">
+        <f>IF(COUNT(P35:Q35)=0,"",ROUND(AVERAGE(P35:Q35),1))</f>
+        <v/>
+      </c>
+      <c r="S35" s="7" t="n"/>
+      <c r="T35" s="7" t="n"/>
+      <c r="U35" s="7" t="n"/>
+      <c r="V35" s="7" t="n"/>
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="8" t="n">
@@ -4104,14 +6226,32 @@
       <c r="C36" s="9" t="n"/>
       <c r="D36" s="9" t="n"/>
       <c r="E36" s="9" t="n"/>
-      <c r="F36" s="9">
-        <f>IF(COUNT(D36:E36)=0,"",ROUND(AVERAGE(D36:E36),1))</f>
-        <v/>
-      </c>
+      <c r="F36" s="9" t="n"/>
       <c r="G36" s="9" t="n"/>
       <c r="H36" s="9" t="n"/>
       <c r="I36" s="9" t="n"/>
       <c r="J36" s="9" t="n"/>
+      <c r="K36" s="9" t="n"/>
+      <c r="L36" s="9" t="n"/>
+      <c r="M36" s="9" t="n"/>
+      <c r="N36" s="9" t="n"/>
+      <c r="O36" s="9" t="n"/>
+      <c r="P36" s="9">
+        <f>IF(COUNT(D36:I36)=0,"",SUM(D36:I36))</f>
+        <v/>
+      </c>
+      <c r="Q36" s="9">
+        <f>IF(COUNT(J36:O36)=0,"",SUM(J36:O36))</f>
+        <v/>
+      </c>
+      <c r="R36" s="9">
+        <f>IF(COUNT(P36:Q36)=0,"",ROUND(AVERAGE(P36:Q36),1))</f>
+        <v/>
+      </c>
+      <c r="S36" s="9" t="n"/>
+      <c r="T36" s="9" t="n"/>
+      <c r="U36" s="9" t="n"/>
+      <c r="V36" s="9" t="n"/>
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="6" t="n">
@@ -4121,14 +6261,32 @@
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7">
-        <f>IF(COUNT(D37:E37)=0,"",ROUND(AVERAGE(D37:E37),1))</f>
-        <v/>
-      </c>
+      <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
       <c r="H37" s="7" t="n"/>
       <c r="I37" s="7" t="n"/>
       <c r="J37" s="7" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="7" t="n"/>
+      <c r="O37" s="7" t="n"/>
+      <c r="P37" s="7">
+        <f>IF(COUNT(D37:I37)=0,"",SUM(D37:I37))</f>
+        <v/>
+      </c>
+      <c r="Q37" s="7">
+        <f>IF(COUNT(J37:O37)=0,"",SUM(J37:O37))</f>
+        <v/>
+      </c>
+      <c r="R37" s="7">
+        <f>IF(COUNT(P37:Q37)=0,"",ROUND(AVERAGE(P37:Q37),1))</f>
+        <v/>
+      </c>
+      <c r="S37" s="7" t="n"/>
+      <c r="T37" s="7" t="n"/>
+      <c r="U37" s="7" t="n"/>
+      <c r="V37" s="7" t="n"/>
     </row>
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="8" t="n">
@@ -4138,14 +6296,32 @@
       <c r="C38" s="9" t="n"/>
       <c r="D38" s="9" t="n"/>
       <c r="E38" s="9" t="n"/>
-      <c r="F38" s="9">
-        <f>IF(COUNT(D38:E38)=0,"",ROUND(AVERAGE(D38:E38),1))</f>
-        <v/>
-      </c>
+      <c r="F38" s="9" t="n"/>
       <c r="G38" s="9" t="n"/>
       <c r="H38" s="9" t="n"/>
       <c r="I38" s="9" t="n"/>
       <c r="J38" s="9" t="n"/>
+      <c r="K38" s="9" t="n"/>
+      <c r="L38" s="9" t="n"/>
+      <c r="M38" s="9" t="n"/>
+      <c r="N38" s="9" t="n"/>
+      <c r="O38" s="9" t="n"/>
+      <c r="P38" s="9">
+        <f>IF(COUNT(D38:I38)=0,"",SUM(D38:I38))</f>
+        <v/>
+      </c>
+      <c r="Q38" s="9">
+        <f>IF(COUNT(J38:O38)=0,"",SUM(J38:O38))</f>
+        <v/>
+      </c>
+      <c r="R38" s="9">
+        <f>IF(COUNT(P38:Q38)=0,"",ROUND(AVERAGE(P38:Q38),1))</f>
+        <v/>
+      </c>
+      <c r="S38" s="9" t="n"/>
+      <c r="T38" s="9" t="n"/>
+      <c r="U38" s="9" t="n"/>
+      <c r="V38" s="9" t="n"/>
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="6" t="n">
@@ -4155,14 +6331,32 @@
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7">
-        <f>IF(COUNT(D39:E39)=0,"",ROUND(AVERAGE(D39:E39),1))</f>
-        <v/>
-      </c>
+      <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
       <c r="H39" s="7" t="n"/>
       <c r="I39" s="7" t="n"/>
       <c r="J39" s="7" t="n"/>
+      <c r="K39" s="7" t="n"/>
+      <c r="L39" s="7" t="n"/>
+      <c r="M39" s="7" t="n"/>
+      <c r="N39" s="7" t="n"/>
+      <c r="O39" s="7" t="n"/>
+      <c r="P39" s="7">
+        <f>IF(COUNT(D39:I39)=0,"",SUM(D39:I39))</f>
+        <v/>
+      </c>
+      <c r="Q39" s="7">
+        <f>IF(COUNT(J39:O39)=0,"",SUM(J39:O39))</f>
+        <v/>
+      </c>
+      <c r="R39" s="7">
+        <f>IF(COUNT(P39:Q39)=0,"",ROUND(AVERAGE(P39:Q39),1))</f>
+        <v/>
+      </c>
+      <c r="S39" s="7" t="n"/>
+      <c r="T39" s="7" t="n"/>
+      <c r="U39" s="7" t="n"/>
+      <c r="V39" s="7" t="n"/>
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="8" t="n">
@@ -4172,14 +6366,32 @@
       <c r="C40" s="9" t="n"/>
       <c r="D40" s="9" t="n"/>
       <c r="E40" s="9" t="n"/>
-      <c r="F40" s="9">
-        <f>IF(COUNT(D40:E40)=0,"",ROUND(AVERAGE(D40:E40),1))</f>
-        <v/>
-      </c>
+      <c r="F40" s="9" t="n"/>
       <c r="G40" s="9" t="n"/>
       <c r="H40" s="9" t="n"/>
       <c r="I40" s="9" t="n"/>
       <c r="J40" s="9" t="n"/>
+      <c r="K40" s="9" t="n"/>
+      <c r="L40" s="9" t="n"/>
+      <c r="M40" s="9" t="n"/>
+      <c r="N40" s="9" t="n"/>
+      <c r="O40" s="9" t="n"/>
+      <c r="P40" s="9">
+        <f>IF(COUNT(D40:I40)=0,"",SUM(D40:I40))</f>
+        <v/>
+      </c>
+      <c r="Q40" s="9">
+        <f>IF(COUNT(J40:O40)=0,"",SUM(J40:O40))</f>
+        <v/>
+      </c>
+      <c r="R40" s="9">
+        <f>IF(COUNT(P40:Q40)=0,"",ROUND(AVERAGE(P40:Q40),1))</f>
+        <v/>
+      </c>
+      <c r="S40" s="9" t="n"/>
+      <c r="T40" s="9" t="n"/>
+      <c r="U40" s="9" t="n"/>
+      <c r="V40" s="9" t="n"/>
     </row>
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="6" t="n">
@@ -4189,14 +6401,32 @@
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
-      <c r="F41" s="7">
-        <f>IF(COUNT(D41:E41)=0,"",ROUND(AVERAGE(D41:E41),1))</f>
-        <v/>
-      </c>
+      <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
       <c r="H41" s="7" t="n"/>
       <c r="I41" s="7" t="n"/>
       <c r="J41" s="7" t="n"/>
+      <c r="K41" s="7" t="n"/>
+      <c r="L41" s="7" t="n"/>
+      <c r="M41" s="7" t="n"/>
+      <c r="N41" s="7" t="n"/>
+      <c r="O41" s="7" t="n"/>
+      <c r="P41" s="7">
+        <f>IF(COUNT(D41:I41)=0,"",SUM(D41:I41))</f>
+        <v/>
+      </c>
+      <c r="Q41" s="7">
+        <f>IF(COUNT(J41:O41)=0,"",SUM(J41:O41))</f>
+        <v/>
+      </c>
+      <c r="R41" s="7">
+        <f>IF(COUNT(P41:Q41)=0,"",ROUND(AVERAGE(P41:Q41),1))</f>
+        <v/>
+      </c>
+      <c r="S41" s="7" t="n"/>
+      <c r="T41" s="7" t="n"/>
+      <c r="U41" s="7" t="n"/>
+      <c r="V41" s="7" t="n"/>
     </row>
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="8" t="n">
@@ -4206,14 +6436,32 @@
       <c r="C42" s="9" t="n"/>
       <c r="D42" s="9" t="n"/>
       <c r="E42" s="9" t="n"/>
-      <c r="F42" s="9">
-        <f>IF(COUNT(D42:E42)=0,"",ROUND(AVERAGE(D42:E42),1))</f>
-        <v/>
-      </c>
+      <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
       <c r="H42" s="9" t="n"/>
       <c r="I42" s="9" t="n"/>
       <c r="J42" s="9" t="n"/>
+      <c r="K42" s="9" t="n"/>
+      <c r="L42" s="9" t="n"/>
+      <c r="M42" s="9" t="n"/>
+      <c r="N42" s="9" t="n"/>
+      <c r="O42" s="9" t="n"/>
+      <c r="P42" s="9">
+        <f>IF(COUNT(D42:I42)=0,"",SUM(D42:I42))</f>
+        <v/>
+      </c>
+      <c r="Q42" s="9">
+        <f>IF(COUNT(J42:O42)=0,"",SUM(J42:O42))</f>
+        <v/>
+      </c>
+      <c r="R42" s="9">
+        <f>IF(COUNT(P42:Q42)=0,"",ROUND(AVERAGE(P42:Q42),1))</f>
+        <v/>
+      </c>
+      <c r="S42" s="9" t="n"/>
+      <c r="T42" s="9" t="n"/>
+      <c r="U42" s="9" t="n"/>
+      <c r="V42" s="9" t="n"/>
     </row>
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="6" t="n">
@@ -4223,14 +6471,32 @@
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7">
-        <f>IF(COUNT(D43:E43)=0,"",ROUND(AVERAGE(D43:E43),1))</f>
-        <v/>
-      </c>
+      <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="7" t="n"/>
       <c r="I43" s="7" t="n"/>
       <c r="J43" s="7" t="n"/>
+      <c r="K43" s="7" t="n"/>
+      <c r="L43" s="7" t="n"/>
+      <c r="M43" s="7" t="n"/>
+      <c r="N43" s="7" t="n"/>
+      <c r="O43" s="7" t="n"/>
+      <c r="P43" s="7">
+        <f>IF(COUNT(D43:I43)=0,"",SUM(D43:I43))</f>
+        <v/>
+      </c>
+      <c r="Q43" s="7">
+        <f>IF(COUNT(J43:O43)=0,"",SUM(J43:O43))</f>
+        <v/>
+      </c>
+      <c r="R43" s="7">
+        <f>IF(COUNT(P43:Q43)=0,"",ROUND(AVERAGE(P43:Q43),1))</f>
+        <v/>
+      </c>
+      <c r="S43" s="7" t="n"/>
+      <c r="T43" s="7" t="n"/>
+      <c r="U43" s="7" t="n"/>
+      <c r="V43" s="7" t="n"/>
     </row>
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="8" t="n">
@@ -4240,14 +6506,32 @@
       <c r="C44" s="9" t="n"/>
       <c r="D44" s="9" t="n"/>
       <c r="E44" s="9" t="n"/>
-      <c r="F44" s="9">
-        <f>IF(COUNT(D44:E44)=0,"",ROUND(AVERAGE(D44:E44),1))</f>
-        <v/>
-      </c>
+      <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n"/>
       <c r="H44" s="9" t="n"/>
       <c r="I44" s="9" t="n"/>
       <c r="J44" s="9" t="n"/>
+      <c r="K44" s="9" t="n"/>
+      <c r="L44" s="9" t="n"/>
+      <c r="M44" s="9" t="n"/>
+      <c r="N44" s="9" t="n"/>
+      <c r="O44" s="9" t="n"/>
+      <c r="P44" s="9">
+        <f>IF(COUNT(D44:I44)=0,"",SUM(D44:I44))</f>
+        <v/>
+      </c>
+      <c r="Q44" s="9">
+        <f>IF(COUNT(J44:O44)=0,"",SUM(J44:O44))</f>
+        <v/>
+      </c>
+      <c r="R44" s="9">
+        <f>IF(COUNT(P44:Q44)=0,"",ROUND(AVERAGE(P44:Q44),1))</f>
+        <v/>
+      </c>
+      <c r="S44" s="9" t="n"/>
+      <c r="T44" s="9" t="n"/>
+      <c r="U44" s="9" t="n"/>
+      <c r="V44" s="9" t="n"/>
     </row>
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="6" t="n">
@@ -4257,14 +6541,32 @@
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
-      <c r="F45" s="7">
-        <f>IF(COUNT(D45:E45)=0,"",ROUND(AVERAGE(D45:E45),1))</f>
-        <v/>
-      </c>
+      <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
       <c r="H45" s="7" t="n"/>
       <c r="I45" s="7" t="n"/>
       <c r="J45" s="7" t="n"/>
+      <c r="K45" s="7" t="n"/>
+      <c r="L45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
+      <c r="N45" s="7" t="n"/>
+      <c r="O45" s="7" t="n"/>
+      <c r="P45" s="7">
+        <f>IF(COUNT(D45:I45)=0,"",SUM(D45:I45))</f>
+        <v/>
+      </c>
+      <c r="Q45" s="7">
+        <f>IF(COUNT(J45:O45)=0,"",SUM(J45:O45))</f>
+        <v/>
+      </c>
+      <c r="R45" s="7">
+        <f>IF(COUNT(P45:Q45)=0,"",ROUND(AVERAGE(P45:Q45),1))</f>
+        <v/>
+      </c>
+      <c r="S45" s="7" t="n"/>
+      <c r="T45" s="7" t="n"/>
+      <c r="U45" s="7" t="n"/>
+      <c r="V45" s="7" t="n"/>
     </row>
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="8" t="n">
@@ -4274,14 +6576,32 @@
       <c r="C46" s="9" t="n"/>
       <c r="D46" s="9" t="n"/>
       <c r="E46" s="9" t="n"/>
-      <c r="F46" s="9">
-        <f>IF(COUNT(D46:E46)=0,"",ROUND(AVERAGE(D46:E46),1))</f>
-        <v/>
-      </c>
+      <c r="F46" s="9" t="n"/>
       <c r="G46" s="9" t="n"/>
       <c r="H46" s="9" t="n"/>
       <c r="I46" s="9" t="n"/>
       <c r="J46" s="9" t="n"/>
+      <c r="K46" s="9" t="n"/>
+      <c r="L46" s="9" t="n"/>
+      <c r="M46" s="9" t="n"/>
+      <c r="N46" s="9" t="n"/>
+      <c r="O46" s="9" t="n"/>
+      <c r="P46" s="9">
+        <f>IF(COUNT(D46:I46)=0,"",SUM(D46:I46))</f>
+        <v/>
+      </c>
+      <c r="Q46" s="9">
+        <f>IF(COUNT(J46:O46)=0,"",SUM(J46:O46))</f>
+        <v/>
+      </c>
+      <c r="R46" s="9">
+        <f>IF(COUNT(P46:Q46)=0,"",ROUND(AVERAGE(P46:Q46),1))</f>
+        <v/>
+      </c>
+      <c r="S46" s="9" t="n"/>
+      <c r="T46" s="9" t="n"/>
+      <c r="U46" s="9" t="n"/>
+      <c r="V46" s="9" t="n"/>
     </row>
     <row r="47" ht="19" customHeight="1">
       <c r="A47" s="6" t="n">
@@ -4291,14 +6611,32 @@
       <c r="C47" s="7" t="n"/>
       <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
-      <c r="F47" s="7">
-        <f>IF(COUNT(D47:E47)=0,"",ROUND(AVERAGE(D47:E47),1))</f>
-        <v/>
-      </c>
+      <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
       <c r="H47" s="7" t="n"/>
       <c r="I47" s="7" t="n"/>
       <c r="J47" s="7" t="n"/>
+      <c r="K47" s="7" t="n"/>
+      <c r="L47" s="7" t="n"/>
+      <c r="M47" s="7" t="n"/>
+      <c r="N47" s="7" t="n"/>
+      <c r="O47" s="7" t="n"/>
+      <c r="P47" s="7">
+        <f>IF(COUNT(D47:I47)=0,"",SUM(D47:I47))</f>
+        <v/>
+      </c>
+      <c r="Q47" s="7">
+        <f>IF(COUNT(J47:O47)=0,"",SUM(J47:O47))</f>
+        <v/>
+      </c>
+      <c r="R47" s="7">
+        <f>IF(COUNT(P47:Q47)=0,"",ROUND(AVERAGE(P47:Q47),1))</f>
+        <v/>
+      </c>
+      <c r="S47" s="7" t="n"/>
+      <c r="T47" s="7" t="n"/>
+      <c r="U47" s="7" t="n"/>
+      <c r="V47" s="7" t="n"/>
     </row>
     <row r="48" ht="19" customHeight="1">
       <c r="A48" s="8" t="n">
@@ -4308,14 +6646,32 @@
       <c r="C48" s="9" t="n"/>
       <c r="D48" s="9" t="n"/>
       <c r="E48" s="9" t="n"/>
-      <c r="F48" s="9">
-        <f>IF(COUNT(D48:E48)=0,"",ROUND(AVERAGE(D48:E48),1))</f>
-        <v/>
-      </c>
+      <c r="F48" s="9" t="n"/>
       <c r="G48" s="9" t="n"/>
       <c r="H48" s="9" t="n"/>
       <c r="I48" s="9" t="n"/>
       <c r="J48" s="9" t="n"/>
+      <c r="K48" s="9" t="n"/>
+      <c r="L48" s="9" t="n"/>
+      <c r="M48" s="9" t="n"/>
+      <c r="N48" s="9" t="n"/>
+      <c r="O48" s="9" t="n"/>
+      <c r="P48" s="9">
+        <f>IF(COUNT(D48:I48)=0,"",SUM(D48:I48))</f>
+        <v/>
+      </c>
+      <c r="Q48" s="9">
+        <f>IF(COUNT(J48:O48)=0,"",SUM(J48:O48))</f>
+        <v/>
+      </c>
+      <c r="R48" s="9">
+        <f>IF(COUNT(P48:Q48)=0,"",ROUND(AVERAGE(P48:Q48),1))</f>
+        <v/>
+      </c>
+      <c r="S48" s="9" t="n"/>
+      <c r="T48" s="9" t="n"/>
+      <c r="U48" s="9" t="n"/>
+      <c r="V48" s="9" t="n"/>
     </row>
     <row r="49" ht="19" customHeight="1">
       <c r="A49" s="6" t="n">
@@ -4325,14 +6681,32 @@
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
-      <c r="F49" s="7">
-        <f>IF(COUNT(D49:E49)=0,"",ROUND(AVERAGE(D49:E49),1))</f>
-        <v/>
-      </c>
+      <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
       <c r="H49" s="7" t="n"/>
       <c r="I49" s="7" t="n"/>
       <c r="J49" s="7" t="n"/>
+      <c r="K49" s="7" t="n"/>
+      <c r="L49" s="7" t="n"/>
+      <c r="M49" s="7" t="n"/>
+      <c r="N49" s="7" t="n"/>
+      <c r="O49" s="7" t="n"/>
+      <c r="P49" s="7">
+        <f>IF(COUNT(D49:I49)=0,"",SUM(D49:I49))</f>
+        <v/>
+      </c>
+      <c r="Q49" s="7">
+        <f>IF(COUNT(J49:O49)=0,"",SUM(J49:O49))</f>
+        <v/>
+      </c>
+      <c r="R49" s="7">
+        <f>IF(COUNT(P49:Q49)=0,"",ROUND(AVERAGE(P49:Q49),1))</f>
+        <v/>
+      </c>
+      <c r="S49" s="7" t="n"/>
+      <c r="T49" s="7" t="n"/>
+      <c r="U49" s="7" t="n"/>
+      <c r="V49" s="7" t="n"/>
     </row>
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="8" t="n">
@@ -4342,14 +6716,32 @@
       <c r="C50" s="9" t="n"/>
       <c r="D50" s="9" t="n"/>
       <c r="E50" s="9" t="n"/>
-      <c r="F50" s="9">
-        <f>IF(COUNT(D50:E50)=0,"",ROUND(AVERAGE(D50:E50),1))</f>
-        <v/>
-      </c>
+      <c r="F50" s="9" t="n"/>
       <c r="G50" s="9" t="n"/>
       <c r="H50" s="9" t="n"/>
       <c r="I50" s="9" t="n"/>
       <c r="J50" s="9" t="n"/>
+      <c r="K50" s="9" t="n"/>
+      <c r="L50" s="9" t="n"/>
+      <c r="M50" s="9" t="n"/>
+      <c r="N50" s="9" t="n"/>
+      <c r="O50" s="9" t="n"/>
+      <c r="P50" s="9">
+        <f>IF(COUNT(D50:I50)=0,"",SUM(D50:I50))</f>
+        <v/>
+      </c>
+      <c r="Q50" s="9">
+        <f>IF(COUNT(J50:O50)=0,"",SUM(J50:O50))</f>
+        <v/>
+      </c>
+      <c r="R50" s="9">
+        <f>IF(COUNT(P50:Q50)=0,"",ROUND(AVERAGE(P50:Q50),1))</f>
+        <v/>
+      </c>
+      <c r="S50" s="9" t="n"/>
+      <c r="T50" s="9" t="n"/>
+      <c r="U50" s="9" t="n"/>
+      <c r="V50" s="9" t="n"/>
     </row>
     <row r="51" ht="19" customHeight="1">
       <c r="A51" s="6" t="n">
@@ -4359,14 +6751,32 @@
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7">
-        <f>IF(COUNT(D51:E51)=0,"",ROUND(AVERAGE(D51:E51),1))</f>
-        <v/>
-      </c>
+      <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="7" t="n"/>
       <c r="I51" s="7" t="n"/>
       <c r="J51" s="7" t="n"/>
+      <c r="K51" s="7" t="n"/>
+      <c r="L51" s="7" t="n"/>
+      <c r="M51" s="7" t="n"/>
+      <c r="N51" s="7" t="n"/>
+      <c r="O51" s="7" t="n"/>
+      <c r="P51" s="7">
+        <f>IF(COUNT(D51:I51)=0,"",SUM(D51:I51))</f>
+        <v/>
+      </c>
+      <c r="Q51" s="7">
+        <f>IF(COUNT(J51:O51)=0,"",SUM(J51:O51))</f>
+        <v/>
+      </c>
+      <c r="R51" s="7">
+        <f>IF(COUNT(P51:Q51)=0,"",ROUND(AVERAGE(P51:Q51),1))</f>
+        <v/>
+      </c>
+      <c r="S51" s="7" t="n"/>
+      <c r="T51" s="7" t="n"/>
+      <c r="U51" s="7" t="n"/>
+      <c r="V51" s="7" t="n"/>
     </row>
     <row r="52" ht="19" customHeight="1">
       <c r="A52" s="8" t="n">
@@ -4376,14 +6786,32 @@
       <c r="C52" s="9" t="n"/>
       <c r="D52" s="9" t="n"/>
       <c r="E52" s="9" t="n"/>
-      <c r="F52" s="9">
-        <f>IF(COUNT(D52:E52)=0,"",ROUND(AVERAGE(D52:E52),1))</f>
-        <v/>
-      </c>
+      <c r="F52" s="9" t="n"/>
       <c r="G52" s="9" t="n"/>
       <c r="H52" s="9" t="n"/>
       <c r="I52" s="9" t="n"/>
       <c r="J52" s="9" t="n"/>
+      <c r="K52" s="9" t="n"/>
+      <c r="L52" s="9" t="n"/>
+      <c r="M52" s="9" t="n"/>
+      <c r="N52" s="9" t="n"/>
+      <c r="O52" s="9" t="n"/>
+      <c r="P52" s="9">
+        <f>IF(COUNT(D52:I52)=0,"",SUM(D52:I52))</f>
+        <v/>
+      </c>
+      <c r="Q52" s="9">
+        <f>IF(COUNT(J52:O52)=0,"",SUM(J52:O52))</f>
+        <v/>
+      </c>
+      <c r="R52" s="9">
+        <f>IF(COUNT(P52:Q52)=0,"",ROUND(AVERAGE(P52:Q52),1))</f>
+        <v/>
+      </c>
+      <c r="S52" s="9" t="n"/>
+      <c r="T52" s="9" t="n"/>
+      <c r="U52" s="9" t="n"/>
+      <c r="V52" s="9" t="n"/>
     </row>
     <row r="53" ht="19" customHeight="1">
       <c r="A53" s="6" t="n">
@@ -4393,14 +6821,32 @@
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7">
-        <f>IF(COUNT(D53:E53)=0,"",ROUND(AVERAGE(D53:E53),1))</f>
-        <v/>
-      </c>
+      <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
       <c r="I53" s="7" t="n"/>
       <c r="J53" s="7" t="n"/>
+      <c r="K53" s="7" t="n"/>
+      <c r="L53" s="7" t="n"/>
+      <c r="M53" s="7" t="n"/>
+      <c r="N53" s="7" t="n"/>
+      <c r="O53" s="7" t="n"/>
+      <c r="P53" s="7">
+        <f>IF(COUNT(D53:I53)=0,"",SUM(D53:I53))</f>
+        <v/>
+      </c>
+      <c r="Q53" s="7">
+        <f>IF(COUNT(J53:O53)=0,"",SUM(J53:O53))</f>
+        <v/>
+      </c>
+      <c r="R53" s="7">
+        <f>IF(COUNT(P53:Q53)=0,"",ROUND(AVERAGE(P53:Q53),1))</f>
+        <v/>
+      </c>
+      <c r="S53" s="7" t="n"/>
+      <c r="T53" s="7" t="n"/>
+      <c r="U53" s="7" t="n"/>
+      <c r="V53" s="7" t="n"/>
     </row>
     <row r="54" ht="19" customHeight="1">
       <c r="A54" s="8" t="n">
@@ -4410,14 +6856,32 @@
       <c r="C54" s="9" t="n"/>
       <c r="D54" s="9" t="n"/>
       <c r="E54" s="9" t="n"/>
-      <c r="F54" s="9">
-        <f>IF(COUNT(D54:E54)=0,"",ROUND(AVERAGE(D54:E54),1))</f>
-        <v/>
-      </c>
+      <c r="F54" s="9" t="n"/>
       <c r="G54" s="9" t="n"/>
       <c r="H54" s="9" t="n"/>
       <c r="I54" s="9" t="n"/>
       <c r="J54" s="9" t="n"/>
+      <c r="K54" s="9" t="n"/>
+      <c r="L54" s="9" t="n"/>
+      <c r="M54" s="9" t="n"/>
+      <c r="N54" s="9" t="n"/>
+      <c r="O54" s="9" t="n"/>
+      <c r="P54" s="9">
+        <f>IF(COUNT(D54:I54)=0,"",SUM(D54:I54))</f>
+        <v/>
+      </c>
+      <c r="Q54" s="9">
+        <f>IF(COUNT(J54:O54)=0,"",SUM(J54:O54))</f>
+        <v/>
+      </c>
+      <c r="R54" s="9">
+        <f>IF(COUNT(P54:Q54)=0,"",ROUND(AVERAGE(P54:Q54),1))</f>
+        <v/>
+      </c>
+      <c r="S54" s="9" t="n"/>
+      <c r="T54" s="9" t="n"/>
+      <c r="U54" s="9" t="n"/>
+      <c r="V54" s="9" t="n"/>
     </row>
     <row r="55" ht="19" customHeight="1">
       <c r="A55" s="6" t="n">
@@ -4427,14 +6891,32 @@
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7">
-        <f>IF(COUNT(D55:E55)=0,"",ROUND(AVERAGE(D55:E55),1))</f>
-        <v/>
-      </c>
+      <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
       <c r="I55" s="7" t="n"/>
       <c r="J55" s="7" t="n"/>
+      <c r="K55" s="7" t="n"/>
+      <c r="L55" s="7" t="n"/>
+      <c r="M55" s="7" t="n"/>
+      <c r="N55" s="7" t="n"/>
+      <c r="O55" s="7" t="n"/>
+      <c r="P55" s="7">
+        <f>IF(COUNT(D55:I55)=0,"",SUM(D55:I55))</f>
+        <v/>
+      </c>
+      <c r="Q55" s="7">
+        <f>IF(COUNT(J55:O55)=0,"",SUM(J55:O55))</f>
+        <v/>
+      </c>
+      <c r="R55" s="7">
+        <f>IF(COUNT(P55:Q55)=0,"",ROUND(AVERAGE(P55:Q55),1))</f>
+        <v/>
+      </c>
+      <c r="S55" s="7" t="n"/>
+      <c r="T55" s="7" t="n"/>
+      <c r="U55" s="7" t="n"/>
+      <c r="V55" s="7" t="n"/>
     </row>
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="8" t="n">
@@ -4444,14 +6926,32 @@
       <c r="C56" s="9" t="n"/>
       <c r="D56" s="9" t="n"/>
       <c r="E56" s="9" t="n"/>
-      <c r="F56" s="9">
-        <f>IF(COUNT(D56:E56)=0,"",ROUND(AVERAGE(D56:E56),1))</f>
-        <v/>
-      </c>
+      <c r="F56" s="9" t="n"/>
       <c r="G56" s="9" t="n"/>
       <c r="H56" s="9" t="n"/>
       <c r="I56" s="9" t="n"/>
       <c r="J56" s="9" t="n"/>
+      <c r="K56" s="9" t="n"/>
+      <c r="L56" s="9" t="n"/>
+      <c r="M56" s="9" t="n"/>
+      <c r="N56" s="9" t="n"/>
+      <c r="O56" s="9" t="n"/>
+      <c r="P56" s="9">
+        <f>IF(COUNT(D56:I56)=0,"",SUM(D56:I56))</f>
+        <v/>
+      </c>
+      <c r="Q56" s="9">
+        <f>IF(COUNT(J56:O56)=0,"",SUM(J56:O56))</f>
+        <v/>
+      </c>
+      <c r="R56" s="9">
+        <f>IF(COUNT(P56:Q56)=0,"",ROUND(AVERAGE(P56:Q56),1))</f>
+        <v/>
+      </c>
+      <c r="S56" s="9" t="n"/>
+      <c r="T56" s="9" t="n"/>
+      <c r="U56" s="9" t="n"/>
+      <c r="V56" s="9" t="n"/>
     </row>
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="6" t="n">
@@ -4461,14 +6961,32 @@
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7">
-        <f>IF(COUNT(D57:E57)=0,"",ROUND(AVERAGE(D57:E57),1))</f>
-        <v/>
-      </c>
+      <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
       <c r="I57" s="7" t="n"/>
       <c r="J57" s="7" t="n"/>
+      <c r="K57" s="7" t="n"/>
+      <c r="L57" s="7" t="n"/>
+      <c r="M57" s="7" t="n"/>
+      <c r="N57" s="7" t="n"/>
+      <c r="O57" s="7" t="n"/>
+      <c r="P57" s="7">
+        <f>IF(COUNT(D57:I57)=0,"",SUM(D57:I57))</f>
+        <v/>
+      </c>
+      <c r="Q57" s="7">
+        <f>IF(COUNT(J57:O57)=0,"",SUM(J57:O57))</f>
+        <v/>
+      </c>
+      <c r="R57" s="7">
+        <f>IF(COUNT(P57:Q57)=0,"",ROUND(AVERAGE(P57:Q57),1))</f>
+        <v/>
+      </c>
+      <c r="S57" s="7" t="n"/>
+      <c r="T57" s="7" t="n"/>
+      <c r="U57" s="7" t="n"/>
+      <c r="V57" s="7" t="n"/>
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="8" t="n">
@@ -4478,14 +6996,32 @@
       <c r="C58" s="9" t="n"/>
       <c r="D58" s="9" t="n"/>
       <c r="E58" s="9" t="n"/>
-      <c r="F58" s="9">
-        <f>IF(COUNT(D58:E58)=0,"",ROUND(AVERAGE(D58:E58),1))</f>
-        <v/>
-      </c>
+      <c r="F58" s="9" t="n"/>
       <c r="G58" s="9" t="n"/>
       <c r="H58" s="9" t="n"/>
       <c r="I58" s="9" t="n"/>
       <c r="J58" s="9" t="n"/>
+      <c r="K58" s="9" t="n"/>
+      <c r="L58" s="9" t="n"/>
+      <c r="M58" s="9" t="n"/>
+      <c r="N58" s="9" t="n"/>
+      <c r="O58" s="9" t="n"/>
+      <c r="P58" s="9">
+        <f>IF(COUNT(D58:I58)=0,"",SUM(D58:I58))</f>
+        <v/>
+      </c>
+      <c r="Q58" s="9">
+        <f>IF(COUNT(J58:O58)=0,"",SUM(J58:O58))</f>
+        <v/>
+      </c>
+      <c r="R58" s="9">
+        <f>IF(COUNT(P58:Q58)=0,"",ROUND(AVERAGE(P58:Q58),1))</f>
+        <v/>
+      </c>
+      <c r="S58" s="9" t="n"/>
+      <c r="T58" s="9" t="n"/>
+      <c r="U58" s="9" t="n"/>
+      <c r="V58" s="9" t="n"/>
     </row>
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="6" t="n">
@@ -4495,14 +7031,32 @@
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7">
-        <f>IF(COUNT(D59:E59)=0,"",ROUND(AVERAGE(D59:E59),1))</f>
-        <v/>
-      </c>
+      <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
       <c r="I59" s="7" t="n"/>
       <c r="J59" s="7" t="n"/>
+      <c r="K59" s="7" t="n"/>
+      <c r="L59" s="7" t="n"/>
+      <c r="M59" s="7" t="n"/>
+      <c r="N59" s="7" t="n"/>
+      <c r="O59" s="7" t="n"/>
+      <c r="P59" s="7">
+        <f>IF(COUNT(D59:I59)=0,"",SUM(D59:I59))</f>
+        <v/>
+      </c>
+      <c r="Q59" s="7">
+        <f>IF(COUNT(J59:O59)=0,"",SUM(J59:O59))</f>
+        <v/>
+      </c>
+      <c r="R59" s="7">
+        <f>IF(COUNT(P59:Q59)=0,"",ROUND(AVERAGE(P59:Q59),1))</f>
+        <v/>
+      </c>
+      <c r="S59" s="7" t="n"/>
+      <c r="T59" s="7" t="n"/>
+      <c r="U59" s="7" t="n"/>
+      <c r="V59" s="7" t="n"/>
     </row>
     <row r="60" ht="19" customHeight="1">
       <c r="A60" s="8" t="n">
@@ -4512,14 +7066,32 @@
       <c r="C60" s="9" t="n"/>
       <c r="D60" s="9" t="n"/>
       <c r="E60" s="9" t="n"/>
-      <c r="F60" s="9">
-        <f>IF(COUNT(D60:E60)=0,"",ROUND(AVERAGE(D60:E60),1))</f>
-        <v/>
-      </c>
+      <c r="F60" s="9" t="n"/>
       <c r="G60" s="9" t="n"/>
       <c r="H60" s="9" t="n"/>
       <c r="I60" s="9" t="n"/>
       <c r="J60" s="9" t="n"/>
+      <c r="K60" s="9" t="n"/>
+      <c r="L60" s="9" t="n"/>
+      <c r="M60" s="9" t="n"/>
+      <c r="N60" s="9" t="n"/>
+      <c r="O60" s="9" t="n"/>
+      <c r="P60" s="9">
+        <f>IF(COUNT(D60:I60)=0,"",SUM(D60:I60))</f>
+        <v/>
+      </c>
+      <c r="Q60" s="9">
+        <f>IF(COUNT(J60:O60)=0,"",SUM(J60:O60))</f>
+        <v/>
+      </c>
+      <c r="R60" s="9">
+        <f>IF(COUNT(P60:Q60)=0,"",ROUND(AVERAGE(P60:Q60),1))</f>
+        <v/>
+      </c>
+      <c r="S60" s="9" t="n"/>
+      <c r="T60" s="9" t="n"/>
+      <c r="U60" s="9" t="n"/>
+      <c r="V60" s="9" t="n"/>
     </row>
     <row r="61" ht="19" customHeight="1">
       <c r="A61" s="6" t="n">
@@ -4529,14 +7101,32 @@
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7">
-        <f>IF(COUNT(D61:E61)=0,"",ROUND(AVERAGE(D61:E61),1))</f>
-        <v/>
-      </c>
+      <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
       <c r="I61" s="7" t="n"/>
       <c r="J61" s="7" t="n"/>
+      <c r="K61" s="7" t="n"/>
+      <c r="L61" s="7" t="n"/>
+      <c r="M61" s="7" t="n"/>
+      <c r="N61" s="7" t="n"/>
+      <c r="O61" s="7" t="n"/>
+      <c r="P61" s="7">
+        <f>IF(COUNT(D61:I61)=0,"",SUM(D61:I61))</f>
+        <v/>
+      </c>
+      <c r="Q61" s="7">
+        <f>IF(COUNT(J61:O61)=0,"",SUM(J61:O61))</f>
+        <v/>
+      </c>
+      <c r="R61" s="7">
+        <f>IF(COUNT(P61:Q61)=0,"",ROUND(AVERAGE(P61:Q61),1))</f>
+        <v/>
+      </c>
+      <c r="S61" s="7" t="n"/>
+      <c r="T61" s="7" t="n"/>
+      <c r="U61" s="7" t="n"/>
+      <c r="V61" s="7" t="n"/>
     </row>
     <row r="62" ht="19" customHeight="1">
       <c r="A62" s="8" t="n">
@@ -4546,21 +7136,39 @@
       <c r="C62" s="9" t="n"/>
       <c r="D62" s="9" t="n"/>
       <c r="E62" s="9" t="n"/>
-      <c r="F62" s="9">
-        <f>IF(COUNT(D62:E62)=0,"",ROUND(AVERAGE(D62:E62),1))</f>
-        <v/>
-      </c>
+      <c r="F62" s="9" t="n"/>
       <c r="G62" s="9" t="n"/>
       <c r="H62" s="9" t="n"/>
       <c r="I62" s="9" t="n"/>
       <c r="J62" s="9" t="n"/>
+      <c r="K62" s="9" t="n"/>
+      <c r="L62" s="9" t="n"/>
+      <c r="M62" s="9" t="n"/>
+      <c r="N62" s="9" t="n"/>
+      <c r="O62" s="9" t="n"/>
+      <c r="P62" s="9">
+        <f>IF(COUNT(D62:I62)=0,"",SUM(D62:I62))</f>
+        <v/>
+      </c>
+      <c r="Q62" s="9">
+        <f>IF(COUNT(J62:O62)=0,"",SUM(J62:O62))</f>
+        <v/>
+      </c>
+      <c r="R62" s="9">
+        <f>IF(COUNT(P62:Q62)=0,"",ROUND(AVERAGE(P62:Q62),1))</f>
+        <v/>
+      </c>
+      <c r="S62" s="9" t="n"/>
+      <c r="T62" s="9" t="n"/>
+      <c r="U62" s="9" t="n"/>
+      <c r="V62" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H3:H62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="T3:T62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"합격,불합격"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6090,12 +8698,12 @@
         </is>
       </c>
       <c r="C4" s="11">
-        <f>COUNTA(창업특강_참석!B3:B92)</f>
+        <f>COUNTA(창업특강_참석!B3:B202)</f>
         <v/>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>명 · 9. 28.(월)</t>
+          <t>명 · 9. 28.(월) 14:00~16:00</t>
         </is>
       </c>
     </row>
@@ -6106,7 +8714,7 @@
         </is>
       </c>
       <c r="C5" s="11">
-        <f>COUNTIF(창업특강_참석!I3:I92,"Y")</f>
+        <f>COUNTIF(창업특강_참석!H3:H202,"Y")</f>
         <v/>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -6170,7 +8778,7 @@
         </is>
       </c>
       <c r="C11" s="11">
-        <f>COUNTIF(서류심사_결과!H3:H62,"합격")</f>
+        <f>COUNTIF(서류심사_결과!T3:T62,"합격")</f>
         <v/>
       </c>
       <c r="D11" s="12" t="inlineStr">

--- a/docs/2026-참석자명단/참가자DB_및_참석자명단.xlsx
+++ b/docs/2026-참석자명단/참가자DB_및_참석자명단.xlsx
@@ -683,7 +683,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>※ 9. 28.(월) 14:00~16:00 현장 서명부(창업특강_참석자명단.pdf)를 받아 이곳에 옮겨 적습니다.</t>
+          <t>※ 9. 28.(월) 12:00~14:00 현장 서명부(창업특강_참석자명단.pdf)를 받아 이곳에 옮겨 적습니다.</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>명 · 9. 28.(월) 14:00~16:00</t>
+          <t>명 · 9. 28.(월) 12:00~14:00</t>
         </is>
       </c>
     </row>
